--- a/文档/生产力造价.xlsx
+++ b/文档/生产力造价.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\Sistine_civ6mod\文档\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04A7A90-820B-4DCD-8CC7-8FF9E7F35DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="奇观" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="292">
   <si>
     <t>BUILDING_STONEHENGE</t>
   </si>
@@ -249,6 +243,12 @@
     <t>BUILDING_SYDNEY_OPERA_HOUSE</t>
   </si>
   <si>
+    <t>&lt;Update&gt;&lt;Where UnitType="</t>
+  </si>
+  <si>
+    <t>原定</t>
+  </si>
+  <si>
     <t>UNIT_SCOUT</t>
   </si>
   <si>
@@ -273,666 +273,650 @@
     <t>BUILDING_WALLS</t>
   </si>
   <si>
+    <t>UNIT_WARRIOR</t>
+  </si>
+  <si>
+    <t>BUILDING_WATER_MILL</t>
+  </si>
+  <si>
+    <t>UNIT_BARBARIAN_HORSEMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_FLOOD_BARRIER</t>
+  </si>
+  <si>
+    <t>UNIT_CREE_OKIHTCITAW</t>
+  </si>
+  <si>
+    <t>BUILDING_PALGUM</t>
+  </si>
+  <si>
+    <t>UNIT_SUMERIAN_WAR_CART</t>
+  </si>
+  <si>
+    <t>BUILDING_BARRACKS</t>
+  </si>
+  <si>
+    <t>UNIT_ARCHER</t>
+  </si>
+  <si>
+    <t>BUILDING_LIBRARY</t>
+  </si>
+  <si>
+    <t>UNIT_MAYAN_HULCHE</t>
+  </si>
+  <si>
+    <t>BUILDING_BASILIKOI_PAIDES</t>
+  </si>
+  <si>
+    <t>UNIT_GAUL_GAESATAE</t>
+  </si>
+  <si>
+    <t>BUILDING_LIGHTHOUSE</t>
+  </si>
+  <si>
+    <t>BUILDING_GROVE</t>
+  </si>
+  <si>
+    <t>UNIT_GALLEY</t>
+  </si>
+  <si>
+    <t>BUILDING_MARKET</t>
+  </si>
+  <si>
+    <t>UNIT_NORWEGIAN_LONGSHIP</t>
+  </si>
+  <si>
+    <t>BUILDING_STABLE</t>
+  </si>
+  <si>
+    <t>UNIT_SPEARMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_TEMPLE</t>
+  </si>
+  <si>
+    <t>UNIT_HEAVY_CHARIOT</t>
+  </si>
+  <si>
+    <t>BUILDING_STAVE_CHURCH</t>
+  </si>
+  <si>
+    <t>UNIT_BATTERING_RAM</t>
+  </si>
+  <si>
+    <t>BUILDING_PRASAT</t>
+  </si>
+  <si>
+    <t>UNIT_GREEK_HOPLITE</t>
+  </si>
+  <si>
+    <t>BUILDING_SUKIENNICE</t>
+  </si>
+  <si>
+    <t>UNIT_AZTEC_EAGLE_WARRIOR</t>
+  </si>
+  <si>
+    <t>BUILDING_ORDU</t>
+  </si>
+  <si>
+    <t>UNIT_PHOENICIA_BIREME</t>
+  </si>
+  <si>
+    <t>BUILDING_TLACHTLI</t>
+  </si>
+  <si>
+    <t>UNIT_NUBIAN_PITATI</t>
+  </si>
+  <si>
+    <t>BUILDING_ARENA</t>
+  </si>
+  <si>
+    <t>UNIT_HORSEMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_AMPHITHEATER</t>
+  </si>
+  <si>
+    <t>UNIT_SWORDSMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_TALL</t>
+  </si>
+  <si>
+    <t>UNIT_EGYPTIAN_CHARIOT_ARCHER</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_WIDE</t>
+  </si>
+  <si>
+    <t>UNIT_WARRIOR_MONK</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_CONQUEST</t>
+  </si>
+  <si>
+    <t>UNIT_SCYTHIAN_HORSE_ARCHER</t>
+  </si>
+  <si>
+    <t>BUILDING_MARAE</t>
+  </si>
+  <si>
+    <t>UNIT_SIEGE_TOWER</t>
+  </si>
+  <si>
+    <t>BUILDING_SHA_COMMISSION</t>
+  </si>
+  <si>
+    <t>UNIT_MACEDONIAN_HYPASPIST</t>
+  </si>
+  <si>
+    <t>BUILDING_CONSULATE</t>
+  </si>
+  <si>
+    <t>UNIT_MACEDONIAN_HETAIROI</t>
+  </si>
+  <si>
+    <t>BUILDING_WORKSHOP</t>
+  </si>
+  <si>
+    <t>UNIT_PERSIAN_IMMORTAL</t>
+  </si>
+  <si>
+    <t>BUILDING_CATHEDRAL</t>
+  </si>
+  <si>
+    <t>BUILDING_ARMORY</t>
+  </si>
+  <si>
+    <t>UNIT_LAHORE_NIHANG</t>
+  </si>
+  <si>
+    <t>BUILDING_GURDWARA</t>
+  </si>
+  <si>
+    <t>UNIT_ROMAN_LEGION</t>
+  </si>
+  <si>
+    <t>BUILDING_MEETING_HOUSE</t>
+  </si>
+  <si>
+    <t>UNIT_KONGO_SHIELD_BEARER</t>
+  </si>
+  <si>
+    <t>BUILDING_MOSQUE</t>
+  </si>
+  <si>
+    <t>UNIT_CATAPULT</t>
+  </si>
+  <si>
+    <t>BUILDING_PAGODA</t>
+  </si>
+  <si>
+    <t>UNIT_QUADRIREME</t>
+  </si>
+  <si>
+    <t>BUILDING_SYNAGOGUE</t>
+  </si>
+  <si>
+    <t>UNIT_INDIAN_VARU</t>
+  </si>
+  <si>
+    <t>BUILDING_WAT</t>
+  </si>
+  <si>
+    <t>UNIT_MAORI_TOA</t>
+  </si>
+  <si>
+    <t>BUILDING_STUPA</t>
+  </si>
+  <si>
+    <t>UNIT_SULEIMAN_JANISSARY</t>
+  </si>
+  <si>
+    <t>BUILDING_DAR_E_MEHR</t>
+  </si>
+  <si>
+    <t>UNIT_BYZANTINE_DROMON</t>
+  </si>
+  <si>
+    <t>UNIT_ZULU_IMPI</t>
+  </si>
+  <si>
+    <t>BUILDING_CASTLE</t>
+  </si>
+  <si>
+    <t>UNIT_CHINESE_CROUCHING_TIGER</t>
+  </si>
+  <si>
+    <t>BUILDING_SEWER</t>
+  </si>
+  <si>
+    <t>BUILDING_QUEENS_BIBLIOTHEQUE</t>
+  </si>
+  <si>
+    <t>UNIT_SKIRMISHER</t>
+  </si>
+  <si>
+    <t>BUILDING_GRAND_BAZAAR</t>
+  </si>
+  <si>
+    <t>UNIT_JAPANESE_SAMURAI</t>
+  </si>
+  <si>
+    <t>BUILDING_UNIVERSITY</t>
+  </si>
+  <si>
+    <t>UNIT_NORWEGIAN_BERSERKER</t>
+  </si>
+  <si>
+    <t>BUILDING_MADRASA</t>
+  </si>
+  <si>
+    <t>UNIT_MAN_AT_ARMS</t>
+  </si>
+  <si>
+    <t>BUILDING_TSIKHE</t>
+  </si>
+  <si>
+    <t>UNIT_MONGOLIAN_KESHIG</t>
+  </si>
+  <si>
+    <t>BUILDING_NAVIGATION_SCHOOL</t>
+  </si>
+  <si>
+    <t>UNIT_GEORGIAN_KHEVSURETI</t>
+  </si>
+  <si>
+    <t>BUILDING_ZOO</t>
+  </si>
+  <si>
+    <t>UNIT_INCA_WARAKAQ</t>
+  </si>
+  <si>
+    <t>BUILDING_THERMAL_BATH</t>
+  </si>
+  <si>
+    <t>UNIT_MILITARY_ENGINEER</t>
+  </si>
+  <si>
+    <t>BUILDING_SHIPYARD</t>
+  </si>
+  <si>
+    <t>UNIT_CROSSBOWMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_BANK</t>
+  </si>
+  <si>
+    <t>UNIT_PIKEMAN</t>
+  </si>
+  <si>
+    <t>BUILDING_MUSEUM_ART</t>
+  </si>
+  <si>
+    <t>UNIT_TREBUCHET</t>
+  </si>
+  <si>
+    <t>BUILDING_MUSEUM_ARTIFACT</t>
+  </si>
+  <si>
+    <t>UNIT_KHMER_DOMREY</t>
+  </si>
+  <si>
+    <t>BUILDING_FERRIS_WHEEL</t>
+  </si>
+  <si>
+    <t>UNIT_COURSER</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_CITYSTATES</t>
+  </si>
+  <si>
+    <t>UNIT_VIETNAMESE_VOI_CHIEN</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_SPIES</t>
+  </si>
+  <si>
+    <t>UNIT_ETHIOPIAN_OROMO_CAVALRY</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_FAITH</t>
+  </si>
+  <si>
+    <t>UNIT_HUNGARY_BLACK_ARMY</t>
+  </si>
+  <si>
+    <t>BUILDING_CHANCERY</t>
+  </si>
+  <si>
+    <t>UNIT_KNIGHT</t>
+  </si>
+  <si>
+    <t>BUILDING_STAR_FORT</t>
+  </si>
+  <si>
+    <t>UNIT_ARABIAN_MAMLUK</t>
+  </si>
+  <si>
+    <t>BUILDING_COAL_POWER_PLANT</t>
+  </si>
+  <si>
+    <t>UNIT_MALI_MANDEKALU_CAVALRY</t>
+  </si>
+  <si>
+    <t>BUILDING_FACTORY</t>
+  </si>
+  <si>
+    <t>UNIT_BYZANTINE_TAGMA</t>
+  </si>
+  <si>
+    <t>BUILDING_ELECTRONICS_FACTORY</t>
+  </si>
+  <si>
+    <t>UNIT_SPY</t>
+  </si>
+  <si>
+    <t>BUILDING_STOCK_EXCHANGE</t>
+  </si>
+  <si>
+    <t>UNIT_MAPUCHE_MALON_RAIDER</t>
+  </si>
+  <si>
+    <t>BUILDING_MILITARY_ACADEMY</t>
+  </si>
+  <si>
+    <t>UNIT_MUSKETMAN</t>
+  </si>
+  <si>
+    <t>UNIT_CARAVEL</t>
+  </si>
+  <si>
+    <t>BUILDING_AQUARIUM</t>
+  </si>
+  <si>
+    <t>BUILDING_SANCTUARY</t>
+  </si>
+  <si>
+    <t>UNIT_OBSERVATION_BALLOON</t>
+  </si>
+  <si>
+    <t>BUILDING_FOSSIL_FUEL_POWER_PLANT</t>
+  </si>
+  <si>
+    <t>BUILDING_OPERA_HOUSE</t>
+  </si>
+  <si>
+    <t>UNIT_OTTOMAN_BARBARY_CORSAIR</t>
+  </si>
+  <si>
+    <t>BUILDING_PUBLIC_SCHOOL</t>
+  </si>
+  <si>
+    <t>UNIT_PORTUGUESE_NAU</t>
+  </si>
+  <si>
+    <t>BUILDING_HANGAR</t>
+  </si>
+  <si>
+    <t>UNIT_SPANISH_CONQUISTADOR</t>
+  </si>
+  <si>
+    <t>BUILDING_FOOD_MARKET</t>
+  </si>
+  <si>
+    <t>UNIT_KOREAN_HWACHA</t>
+  </si>
+  <si>
+    <t>BUILDING_BROADCAST_CENTER</t>
+  </si>
+  <si>
+    <t>UNIT_PIKE_AND_SHOT</t>
+  </si>
+  <si>
+    <t>BUILDING_FILM_STUDIO</t>
+  </si>
+  <si>
+    <t>BUILDING_SEAPORT</t>
+  </si>
+  <si>
+    <t>UNIT_SWEDEN_CAROLEAN</t>
+  </si>
+  <si>
+    <t>BUILDING_RESEARCH_LAB</t>
+  </si>
+  <si>
+    <t>UNIT_BOMBARD</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_MILITARY</t>
+  </si>
+  <si>
+    <t>UNIT_FRIGATE</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_CULTURE</t>
+  </si>
+  <si>
+    <t>UNIT_PRIVATEER</t>
+  </si>
+  <si>
+    <t>BUILDING_GOV_SCIENCE</t>
+  </si>
+  <si>
+    <t>UNIT_ENGLISH_SEADOG</t>
+  </si>
+  <si>
+    <t>BUILDING_SHOPPING_MALL</t>
+  </si>
+  <si>
+    <t>UNIT_DE_ZEVEN_PROVINCIEN</t>
+  </si>
+  <si>
+    <t>BUILDING_HYDROELECTRIC_DAM</t>
+  </si>
+  <si>
+    <t>UNIT_CANADA_MOUNTIE</t>
+  </si>
+  <si>
+    <t>UNIT_INDONESIAN_JONG</t>
+  </si>
+  <si>
+    <t>BUILDING_POWER_PLANT</t>
+  </si>
+  <si>
+    <t>UNIT_FIELD_CANNON</t>
+  </si>
+  <si>
+    <t>BUILDING_AIRPORT</t>
+  </si>
+  <si>
+    <t>BUILDING_STADIUM</t>
+  </si>
+  <si>
+    <t>UNIT_CAVALRY</t>
+  </si>
+  <si>
+    <t>UNIT_POLISH_HUSSAR</t>
+  </si>
+  <si>
+    <t>BUILDING_AQUATICS_CENTER</t>
+  </si>
+  <si>
+    <t>UNIT_CUIRASSIER</t>
+  </si>
+  <si>
+    <t>UNIT_COLOMBIAN_LLANERO</t>
+  </si>
+  <si>
+    <t>UNIT_HUNGARY_HUSZAR</t>
+  </si>
+  <si>
+    <t>BUILDING_MANUFACTURING_PLANT</t>
+  </si>
+  <si>
+    <t>UNIT_RUSSIAN_COSSACK</t>
+  </si>
+  <si>
+    <t>UNIT_ENGLISH_REDCOAT</t>
+  </si>
+  <si>
+    <t>UNIT_FRENCH_GARDE_IMPERIALE</t>
+  </si>
+  <si>
+    <t>UNIT_LINE_INFANTRY</t>
+  </si>
+  <si>
+    <t>UNIT_MEDIC</t>
+  </si>
+  <si>
+    <t>UNIT_IRONCLAD</t>
+  </si>
+  <si>
+    <t>UNIT_RANGER</t>
+  </si>
+  <si>
+    <t>UNIT_SCOTTISH_HIGHLANDER</t>
+  </si>
+  <si>
+    <t>UNIT_AMERICAN_ROUGH_RIDER</t>
+  </si>
+  <si>
+    <t>UNIT_AT_CREW</t>
+  </si>
+  <si>
+    <t>UNIT_DRONE</t>
+  </si>
+  <si>
+    <t>UNIT_BIPLANE</t>
+  </si>
+  <si>
+    <t>UNIT_INFANTRY</t>
+  </si>
+  <si>
+    <t>UNIT_ARTILLERY</t>
+  </si>
+  <si>
+    <t>UNIT_BATTLESHIP</t>
+  </si>
+  <si>
+    <t>UNIT_BRAZILIAN_MINAS_GERAES</t>
+  </si>
+  <si>
+    <t>UNIT_GERMAN_UBOAT</t>
+  </si>
+  <si>
+    <t>UNIT_DIGGER</t>
+  </si>
+  <si>
+    <t>UNIT_SUPPLY_CONVOY</t>
+  </si>
+  <si>
+    <t>UNIT_ANTIAIR_GUN</t>
+  </si>
+  <si>
+    <t>UNIT_SUBMARINE</t>
+  </si>
+  <si>
+    <t>UNIT_TANK</t>
+  </si>
+  <si>
+    <t>UNIT_FIGHTER</t>
+  </si>
+  <si>
+    <t>UNIT_AMERICAN_P51</t>
+  </si>
+  <si>
+    <t>UNIT_SPEC_OPS</t>
+  </si>
+  <si>
+    <t>UNIT_MACHINE_GUN</t>
+  </si>
+  <si>
+    <t>UNIT_AIRCRAFT_CARRIER</t>
+  </si>
+  <si>
+    <t>UNIT_DESTROYER</t>
+  </si>
+  <si>
+    <t>UNIT_BOMBER</t>
+  </si>
+  <si>
+    <t>UNIT_MODERN_AT</t>
+  </si>
+  <si>
+    <t>UNIT_MOBILE_SAM</t>
+  </si>
+  <si>
+    <t>UNIT_HELICOPTER</t>
+  </si>
+  <si>
+    <t>UNIT_MECHANIZED_INFANTRY</t>
+  </si>
+  <si>
+    <t>UNIT_JET_FIGHTER</t>
+  </si>
+  <si>
+    <t>UNIT_NUCLEAR_SUBMARINE</t>
+  </si>
+  <si>
+    <t>UNIT_ROCKET_ARTILLERY</t>
+  </si>
+  <si>
+    <t>UNIT_MISSILE_CRUISER</t>
+  </si>
+  <si>
+    <t>UNIT_MODERN_ARMOR</t>
+  </si>
+  <si>
     <t>UNIT_TRADER</t>
   </si>
   <si>
-    <t>BUILDING_WATER_MILL</t>
-  </si>
-  <si>
-    <t>UNIT_WARRIOR</t>
-  </si>
-  <si>
-    <t>BUILDING_FLOOD_BARRIER</t>
-  </si>
-  <si>
-    <t>UNIT_BARBARIAN_HORSEMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_PALGUM</t>
-  </si>
-  <si>
-    <t>UNIT_CREE_OKIHTCITAW</t>
-  </si>
-  <si>
-    <t>BUILDING_BARRACKS</t>
-  </si>
-  <si>
     <t>UNIT_BUILDER</t>
   </si>
   <si>
-    <t>BUILDING_LIBRARY</t>
-  </si>
-  <si>
-    <t>UNIT_SUMERIAN_WAR_CART</t>
-  </si>
-  <si>
-    <t>BUILDING_BASILIKOI_PAIDES</t>
-  </si>
-  <si>
-    <t>UNIT_ARCHER</t>
-  </si>
-  <si>
-    <t>BUILDING_LIGHTHOUSE</t>
-  </si>
-  <si>
-    <t>UNIT_MAYAN_HULCHE</t>
-  </si>
-  <si>
-    <t>BUILDING_MARKET</t>
-  </si>
-  <si>
-    <t>UNIT_GAUL_GAESATAE</t>
-  </si>
-  <si>
-    <t>BUILDING_STABLE</t>
-  </si>
-  <si>
-    <t>UNIT_GALLEY</t>
-  </si>
-  <si>
-    <t>BUILDING_TEMPLE</t>
-  </si>
-  <si>
-    <t>UNIT_NORWEGIAN_LONGSHIP</t>
-  </si>
-  <si>
-    <t>BUILDING_STAVE_CHURCH</t>
-  </si>
-  <si>
-    <t>UNIT_SPEARMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_PRASAT</t>
-  </si>
-  <si>
-    <t>UNIT_HEAVY_CHARIOT</t>
-  </si>
-  <si>
-    <t>BUILDING_SUKIENNICE</t>
-  </si>
-  <si>
-    <t>UNIT_BATTERING_RAM</t>
-  </si>
-  <si>
-    <t>BUILDING_ORDU</t>
-  </si>
-  <si>
-    <t>UNIT_GREEK_HOPLITE</t>
-  </si>
-  <si>
-    <t>BUILDING_TLACHTLI</t>
-  </si>
-  <si>
-    <t>UNIT_AZTEC_EAGLE_WARRIOR</t>
-  </si>
-  <si>
-    <t>BUILDING_ARENA</t>
-  </si>
-  <si>
-    <t>UNIT_PHOENICIA_BIREME</t>
-  </si>
-  <si>
-    <t>BUILDING_AMPHITHEATER</t>
-  </si>
-  <si>
-    <t>UNIT_NUBIAN_PITATI</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_TALL</t>
+    <t>UNIT_GURU</t>
   </si>
   <si>
     <t>UNIT_MISSIONARY</t>
   </si>
   <si>
-    <t>BUILDING_GOV_WIDE</t>
-  </si>
-  <si>
     <t>UNIT_INQUISITOR</t>
   </si>
   <si>
-    <t>BUILDING_GOV_CONQUEST</t>
-  </si>
-  <si>
     <t>UNIT_SETTLER</t>
   </si>
   <si>
-    <t>BUILDING_MARAE</t>
-  </si>
-  <si>
-    <t>UNIT_HORSEMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_SHA_COMMISSION</t>
-  </si>
-  <si>
-    <t>UNIT_SWORDSMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_GROVE</t>
-  </si>
-  <si>
-    <t>UNIT_EGYPTIAN_CHARIOT_ARCHER</t>
-  </si>
-  <si>
-    <t>BUILDING_CONSULATE</t>
-  </si>
-  <si>
-    <t>UNIT_WARRIOR_MONK</t>
-  </si>
-  <si>
-    <t>BUILDING_CATHEDRAL</t>
-  </si>
-  <si>
-    <t>UNIT_SCYTHIAN_HORSE_ARCHER</t>
-  </si>
-  <si>
-    <t>BUILDING_GURDWARA</t>
-  </si>
-  <si>
-    <t>UNIT_SIEGE_TOWER</t>
-  </si>
-  <si>
-    <t>BUILDING_MEETING_HOUSE</t>
-  </si>
-  <si>
-    <t>UNIT_MACEDONIAN_HYPASPIST</t>
-  </si>
-  <si>
-    <t>BUILDING_MOSQUE</t>
-  </si>
-  <si>
-    <t>UNIT_MACEDONIAN_HETAIROI</t>
-  </si>
-  <si>
-    <t>BUILDING_PAGODA</t>
-  </si>
-  <si>
-    <t>UNIT_PERSIAN_IMMORTAL</t>
-  </si>
-  <si>
-    <t>BUILDING_SYNAGOGUE</t>
-  </si>
-  <si>
-    <t>UNIT_LAHORE_NIHANG</t>
-  </si>
-  <si>
-    <t>BUILDING_WAT</t>
-  </si>
-  <si>
-    <t>UNIT_ROMAN_LEGION</t>
-  </si>
-  <si>
-    <t>BUILDING_STUPA</t>
-  </si>
-  <si>
-    <t>UNIT_KONGO_SHIELD_BEARER</t>
-  </si>
-  <si>
-    <t>BUILDING_DAR_E_MEHR</t>
-  </si>
-  <si>
-    <t>UNIT_GURU</t>
-  </si>
-  <si>
-    <t>BUILDING_WORKSHOP</t>
-  </si>
-  <si>
-    <t>UNIT_CATAPULT</t>
-  </si>
-  <si>
-    <t>BUILDING_ARMORY</t>
-  </si>
-  <si>
-    <t>UNIT_QUADRIREME</t>
-  </si>
-  <si>
-    <t>BUILDING_SEWER</t>
-  </si>
-  <si>
-    <t>UNIT_INDIAN_VARU</t>
-  </si>
-  <si>
-    <t>BUILDING_QUEENS_BIBLIOTHEQUE</t>
-  </si>
-  <si>
-    <t>UNIT_MAORI_TOA</t>
-  </si>
-  <si>
-    <t>BUILDING_CASTLE</t>
-  </si>
-  <si>
-    <t>UNIT_SULEIMAN_JANISSARY</t>
-  </si>
-  <si>
-    <t>BUILDING_GRAND_BAZAAR</t>
-  </si>
-  <si>
-    <t>UNIT_BYZANTINE_DROMON</t>
-  </si>
-  <si>
-    <t>BUILDING_UNIVERSITY</t>
-  </si>
-  <si>
-    <t>UNIT_ZULU_IMPI</t>
-  </si>
-  <si>
-    <t>BUILDING_MADRASA</t>
-  </si>
-  <si>
-    <t>UNIT_CHINESE_CROUCHING_TIGER</t>
-  </si>
-  <si>
-    <t>BUILDING_NAVIGATION_SCHOOL</t>
-  </si>
-  <si>
-    <t>UNIT_SKIRMISHER</t>
-  </si>
-  <si>
-    <t>BUILDING_TSIKHE</t>
-  </si>
-  <si>
-    <t>UNIT_JAPANESE_SAMURAI</t>
-  </si>
-  <si>
-    <t>BUILDING_SHIPYARD</t>
-  </si>
-  <si>
-    <t>UNIT_NORWEGIAN_BERSERKER</t>
-  </si>
-  <si>
-    <t>BUILDING_BANK</t>
-  </si>
-  <si>
-    <t>UNIT_MAN_AT_ARMS</t>
-  </si>
-  <si>
-    <t>BUILDING_MUSEUM_ART</t>
-  </si>
-  <si>
-    <t>UNIT_MONGOLIAN_KESHIG</t>
-  </si>
-  <si>
-    <t>BUILDING_MUSEUM_ARTIFACT</t>
-  </si>
-  <si>
-    <t>UNIT_GEORGIAN_KHEVSURETI</t>
-  </si>
-  <si>
-    <t>BUILDING_FERRIS_WHEEL</t>
-  </si>
-  <si>
-    <t>UNIT_INCA_WARAKAQ</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_CITYSTATES</t>
-  </si>
-  <si>
-    <t>UNIT_MILITARY_ENGINEER</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_SPIES</t>
-  </si>
-  <si>
-    <t>UNIT_CROSSBOWMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_FAITH</t>
-  </si>
-  <si>
-    <t>UNIT_PIKEMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_CHANCERY</t>
-  </si>
-  <si>
     <t>UNIT_APOSTLE</t>
   </si>
   <si>
-    <t>BUILDING_STAR_FORT</t>
-  </si>
-  <si>
-    <t>UNIT_TREBUCHET</t>
-  </si>
-  <si>
-    <t>BUILDING_COAL_POWER_PLANT</t>
-  </si>
-  <si>
-    <t>UNIT_KHMER_DOMREY</t>
-  </si>
-  <si>
-    <t>BUILDING_FACTORY</t>
-  </si>
-  <si>
-    <t>UNIT_COURSER</t>
-  </si>
-  <si>
-    <t>BUILDING_ELECTRONICS_FACTORY</t>
-  </si>
-  <si>
-    <t>UNIT_VIETNAMESE_VOI_CHIEN</t>
-  </si>
-  <si>
-    <t>BUILDING_STOCK_EXCHANGE</t>
-  </si>
-  <si>
-    <t>UNIT_ETHIOPIAN_OROMO_CAVALRY</t>
-  </si>
-  <si>
-    <t>BUILDING_MILITARY_ACADEMY</t>
-  </si>
-  <si>
-    <t>UNIT_HUNGARY_BLACK_ARMY</t>
-  </si>
-  <si>
-    <t>BUILDING_ZOO</t>
-  </si>
-  <si>
-    <t>UNIT_KNIGHT</t>
-  </si>
-  <si>
-    <t>BUILDING_AQUARIUM</t>
-  </si>
-  <si>
-    <t>UNIT_ARABIAN_MAMLUK</t>
-  </si>
-  <si>
-    <t>BUILDING_FOSSIL_FUEL_POWER_PLANT</t>
-  </si>
-  <si>
-    <t>UNIT_MALI_MANDEKALU_CAVALRY</t>
-  </si>
-  <si>
-    <t>BUILDING_THERMAL_BATH</t>
-  </si>
-  <si>
-    <t>UNIT_BYZANTINE_TAGMA</t>
-  </si>
-  <si>
-    <t>BUILDING_HANGAR</t>
-  </si>
-  <si>
-    <t>UNIT_SPY</t>
-  </si>
-  <si>
-    <t>BUILDING_FOOD_MARKET</t>
-  </si>
-  <si>
-    <t>UNIT_MAPUCHE_MALON_RAIDER</t>
-  </si>
-  <si>
-    <t>BUILDING_BROADCAST_CENTER</t>
-  </si>
-  <si>
-    <t>UNIT_MUSKETMAN</t>
-  </si>
-  <si>
-    <t>BUILDING_FILM_STUDIO</t>
-  </si>
-  <si>
-    <t>UNIT_CARAVEL</t>
-  </si>
-  <si>
-    <t>BUILDING_RESEARCH_LAB</t>
-  </si>
-  <si>
-    <t>UNIT_OBSERVATION_BALLOON</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_MILITARY</t>
-  </si>
-  <si>
-    <t>UNIT_OTTOMAN_BARBARY_CORSAIR</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_CULTURE</t>
-  </si>
-  <si>
-    <t>UNIT_PORTUGUESE_NAU</t>
-  </si>
-  <si>
-    <t>BUILDING_GOV_SCIENCE</t>
-  </si>
-  <si>
-    <t>UNIT_SPANISH_CONQUISTADOR</t>
-  </si>
-  <si>
-    <t>BUILDING_SHOPPING_MALL</t>
-  </si>
-  <si>
-    <t>UNIT_KOREAN_HWACHA</t>
-  </si>
-  <si>
-    <t>BUILDING_HYDROELECTRIC_DAM</t>
-  </si>
-  <si>
-    <t>UNIT_PIKE_AND_SHOT</t>
-  </si>
-  <si>
-    <t>BUILDING_SANCTUARY</t>
-  </si>
-  <si>
-    <t>UNIT_SWEDEN_CAROLEAN</t>
-  </si>
-  <si>
-    <t>BUILDING_POWER_PLANT</t>
-  </si>
-  <si>
-    <t>UNIT_BOMBARD</t>
-  </si>
-  <si>
-    <t>BUILDING_AIRPORT</t>
-  </si>
-  <si>
-    <t>UNIT_FRIGATE</t>
-  </si>
-  <si>
-    <t>BUILDING_STADIUM</t>
-  </si>
-  <si>
-    <t>UNIT_PRIVATEER</t>
-  </si>
-  <si>
-    <t>BUILDING_AQUATICS_CENTER</t>
-  </si>
-  <si>
-    <t>UNIT_ENGLISH_SEADOG</t>
-  </si>
-  <si>
-    <t>UNIT_DE_ZEVEN_PROVINCIEN</t>
-  </si>
-  <si>
-    <t>UNIT_CANADA_MOUNTIE</t>
+    <t>UNIT_ROCK_BAND</t>
   </si>
   <si>
     <t>UNIT_NATURALIST</t>
   </si>
   <si>
-    <t>UNIT_INDONESIAN_JONG</t>
-  </si>
-  <si>
-    <t>UNIT_ROCK_BAND</t>
-  </si>
-  <si>
-    <t>UNIT_FIELD_CANNON</t>
-  </si>
-  <si>
-    <t>UNIT_CAVALRY</t>
-  </si>
-  <si>
-    <t>UNIT_POLISH_HUSSAR</t>
-  </si>
-  <si>
-    <t>UNIT_CUIRASSIER</t>
-  </si>
-  <si>
-    <t>UNIT_COLOMBIAN_LLANERO</t>
-  </si>
-  <si>
-    <t>UNIT_HUNGARY_HUSZAR</t>
-  </si>
-  <si>
-    <t>UNIT_RUSSIAN_COSSACK</t>
-  </si>
-  <si>
-    <t>UNIT_ENGLISH_REDCOAT</t>
-  </si>
-  <si>
-    <t>UNIT_FRENCH_GARDE_IMPERIALE</t>
-  </si>
-  <si>
-    <t>UNIT_LINE_INFANTRY</t>
-  </si>
-  <si>
-    <t>UNIT_MEDIC</t>
-  </si>
-  <si>
-    <t>UNIT_IRONCLAD</t>
-  </si>
-  <si>
-    <t>UNIT_RANGER</t>
-  </si>
-  <si>
-    <t>UNIT_SCOTTISH_HIGHLANDER</t>
-  </si>
-  <si>
-    <t>UNIT_AMERICAN_ROUGH_RIDER</t>
-  </si>
-  <si>
     <t>UNIT_ARCHAEOLOGIST</t>
   </si>
   <si>
-    <t>UNIT_AT_CREW</t>
-  </si>
-  <si>
-    <t>UNIT_DRONE</t>
-  </si>
-  <si>
-    <t>UNIT_BIPLANE</t>
-  </si>
-  <si>
-    <t>UNIT_INFANTRY</t>
-  </si>
-  <si>
-    <t>UNIT_ARTILLERY</t>
-  </si>
-  <si>
-    <t>UNIT_BATTLESHIP</t>
-  </si>
-  <si>
-    <t>UNIT_BRAZILIAN_MINAS_GERAES</t>
-  </si>
-  <si>
-    <t>UNIT_GERMAN_UBOAT</t>
-  </si>
-  <si>
-    <t>UNIT_DIGGER</t>
-  </si>
-  <si>
-    <t>UNIT_SUPPLY_CONVOY</t>
-  </si>
-  <si>
-    <t>UNIT_ANTIAIR_GUN</t>
-  </si>
-  <si>
-    <t>UNIT_SUBMARINE</t>
-  </si>
-  <si>
-    <t>UNIT_TANK</t>
-  </si>
-  <si>
-    <t>UNIT_FIGHTER</t>
-  </si>
-  <si>
-    <t>UNIT_AMERICAN_P51</t>
-  </si>
-  <si>
-    <t>UNIT_SPEC_OPS</t>
-  </si>
-  <si>
-    <t>UNIT_MACHINE_GUN</t>
-  </si>
-  <si>
-    <t>UNIT_AIRCRAFT_CARRIER</t>
-  </si>
-  <si>
-    <t>UNIT_DESTROYER</t>
-  </si>
-  <si>
-    <t>UNIT_BOMBER</t>
-  </si>
-  <si>
-    <t>UNIT_MODERN_AT</t>
-  </si>
-  <si>
-    <t>UNIT_MOBILE_SAM</t>
-  </si>
-  <si>
-    <t>UNIT_HELICOPTER</t>
-  </si>
-  <si>
-    <t>UNIT_MECHANIZED_INFANTRY</t>
-  </si>
-  <si>
-    <t>UNIT_JET_FIGHTER</t>
-  </si>
-  <si>
-    <t>UNIT_NUCLEAR_SUBMARINE</t>
-  </si>
-  <si>
-    <t>UNIT_ROCKET_ARTILLERY</t>
-  </si>
-  <si>
-    <t>UNIT_MISSILE_CRUISER</t>
-  </si>
-  <si>
-    <t>UNIT_MODERN_ARMOR</t>
-  </si>
-  <si>
-    <t>&lt;Update&gt;&lt;Where UnitType="</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>COST_PROGRESSION_GAME_PROGRESS</t>
   </si>
   <si>
     <t>COST_PROGRESSION_PREVIOUS_COPIES</t>
-  </si>
-  <si>
-    <t>BUILDING_HOSPITAL</t>
-  </si>
-  <si>
-    <t>BUILDING_OPERA_HOUSE</t>
-  </si>
-  <si>
-    <t>BUILDING_PUBLIC_SCHOOL</t>
-  </si>
-  <si>
-    <t>BUILDING_SEAPORT</t>
-  </si>
-  <si>
-    <t>BUILDING_MEDICAL_LAB</t>
-  </si>
-  <si>
-    <t>BUILDING_MANUFACTURING_PLANT</t>
-  </si>
-  <si>
-    <t>&lt;Update&gt;&lt;Where BuildingType="</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UNIT_MISSIONARY</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>原定</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -941,29 +925,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -971,9 +1278,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -981,21 +1530,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1253,24 +1846,23 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625"/>
-    <col min="10" max="10" width="0" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="46.21875" hidden="1" customWidth="1"/>
-    <col min="12" max="13" width="9" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="0" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="12.6666666666667"/>
+    <col min="10" max="10" width="9" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="46.2166666666667" hidden="1" customWidth="1"/>
+    <col min="12" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1887,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STONEHENGE" /&gt;&lt;Set Cost="150"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -1311,7 +1903,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HANGING_GARDENS" /&gt;&lt;Set Cost="150"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -1327,7 +1919,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TEMPLE_ARTEMIS" /&gt;&lt;Set Cost="150"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1343,7 +1935,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GREAT_BATH" /&gt;&lt;Set Cost="150"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1359,7 +1951,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PYRAMIDS" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1387,7 +1979,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ETEMENANKI" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1422,7 +2014,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ORACLE" /&gt;&lt;Set Cost="250"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1457,7 +2049,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GREAT_LIGHTHOUSE" /&gt;&lt;Set Cost="250"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +2064,7 @@
         <v>18</v>
       </c>
       <c r="F9">
-        <f>建筑单位!P31</f>
+        <f>建筑单位!P30</f>
         <v>195</v>
       </c>
       <c r="G9">
@@ -1492,7 +2084,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_COLOSSUS" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1507,7 +2099,7 @@
         <v>20</v>
       </c>
       <c r="F10">
-        <f>建筑单位!P54</f>
+        <f>建筑单位!P53</f>
         <v>290</v>
       </c>
       <c r="G10">
@@ -1527,7 +2119,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PETRA" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1542,7 +2134,7 @@
         <v>22</v>
       </c>
       <c r="F11">
-        <f>建筑单位!P64</f>
+        <f>建筑单位!P63</f>
         <v>400</v>
       </c>
       <c r="G11">
@@ -1562,7 +2154,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_COLOSSEUM" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1577,7 +2169,7 @@
         <v>24</v>
       </c>
       <c r="F12">
-        <f>建筑单位!P78</f>
+        <f>建筑单位!P77</f>
         <v>520</v>
       </c>
       <c r="G12">
@@ -1597,7 +2189,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GREAT_LIBRARY" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -1612,7 +2204,7 @@
         <v>26</v>
       </c>
       <c r="F13">
-        <f>建筑单位!P84</f>
+        <f>建筑单位!P82</f>
         <v>650</v>
       </c>
       <c r="G13">
@@ -1632,7 +2224,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MAHABODHI_TEMPLE" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -1647,7 +2239,7 @@
         <v>28</v>
       </c>
       <c r="F14">
-        <f>建筑单位!P87</f>
+        <f>建筑单位!P85</f>
         <v>785</v>
       </c>
       <c r="G14">
@@ -1667,7 +2259,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TERRACOTTA_ARMY" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -1683,7 +2275,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_JEBEL_BARKAL" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1699,7 +2291,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_APADANA" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1724,7 +2316,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HALICARNASSUS_MAUSOLEUM" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1746,14 +2338,14 @@
       </c>
       <c r="H18">
         <f>G18/F18</f>
-        <v>0.83333333333333337</v>
+        <v>0.833333333333333</v>
       </c>
       <c r="O18" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MACHU_PICCHU" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1775,14 +2367,14 @@
       </c>
       <c r="H19">
         <f t="shared" ref="H19:H29" si="5">G19/F19</f>
-        <v>0.79545454545454541</v>
+        <v>0.795454545454545</v>
       </c>
       <c r="O19" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STATUE_OF_ZEUS" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1804,14 +2396,14 @@
       </c>
       <c r="H20">
         <f t="shared" si="5"/>
-        <v>0.86206896551724133</v>
+        <v>0.862068965517241</v>
       </c>
       <c r="O20" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HAGIA_SOPHIA" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -1840,7 +2432,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ALHAMBRA" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -1869,7 +2461,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CHICHEN_ITZA" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1891,14 +2483,14 @@
       </c>
       <c r="H23">
         <f t="shared" si="5"/>
-        <v>0.65217391304347827</v>
+        <v>0.652173913043478</v>
       </c>
       <c r="O23" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MONT_ST_MICHEL" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>41</v>
       </c>
@@ -1920,14 +2512,14 @@
       </c>
       <c r="H24">
         <f t="shared" si="5"/>
-        <v>0.68396226415094341</v>
+        <v>0.683962264150943</v>
       </c>
       <c r="O24" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HUEY_TEOCALLI" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -1949,14 +2541,14 @@
       </c>
       <c r="H25">
         <f t="shared" si="5"/>
-        <v>0.68548387096774188</v>
+        <v>0.685483870967742</v>
       </c>
       <c r="O25" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ANGKOR_WAT" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>43</v>
       </c>
@@ -1978,14 +2570,14 @@
       </c>
       <c r="H26">
         <f t="shared" si="5"/>
-        <v>0.68965517241379315</v>
+        <v>0.689655172413793</v>
       </c>
       <c r="O26" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_KILWA_KISIWANI" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>44</v>
       </c>
@@ -2007,14 +2599,14 @@
       </c>
       <c r="H27">
         <f t="shared" si="5"/>
-        <v>0.79012345679012341</v>
+        <v>0.790123456790123</v>
       </c>
       <c r="O27" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_KOTOKU_IN" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -2036,14 +2628,14 @@
       </c>
       <c r="H28">
         <f t="shared" si="5"/>
-        <v>0.78448275862068961</v>
+        <v>0.78448275862069</v>
       </c>
       <c r="O28" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MEENAKSHI_TEMPLE" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>46</v>
       </c>
@@ -2065,14 +2657,14 @@
       </c>
       <c r="H29">
         <f t="shared" si="5"/>
-        <v>0.8783783783783784</v>
+        <v>0.878378378378378</v>
       </c>
       <c r="O29" t="str">
         <f t="shared" si="1"/>
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_UNIVERSITY_SANKORE" /&gt;&lt;Set Cost="480"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>47</v>
       </c>
@@ -2088,7 +2680,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_VENETIAN_ARSENAL" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -2104,7 +2696,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GREAT_ZIMBABWE" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -2120,7 +2712,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FORBIDDEN_CITY" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>50</v>
       </c>
@@ -2136,7 +2728,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CASA_DE_CONTRATACION" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>51</v>
       </c>
@@ -2152,7 +2744,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ST_BASILS_CATHEDRAL" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>52</v>
       </c>
@@ -2168,7 +2760,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TAJ_MAHAL" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>53</v>
       </c>
@@ -2184,7 +2776,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ORSZAGHAZ" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>54</v>
       </c>
@@ -2200,7 +2792,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PANAMA_CANAL" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>55</v>
       </c>
@@ -2216,7 +2808,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TORRE_DE_BELEM" /&gt;&lt;Set Cost="600"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>56</v>
       </c>
@@ -2232,7 +2824,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_POTALA_PALACE" /&gt;&lt;Set Cost="725"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>57</v>
       </c>
@@ -2248,7 +2840,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_RUHR_VALLEY" /&gt;&lt;Set Cost="850"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>58</v>
       </c>
@@ -2264,7 +2856,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BOLSHOI_THEATRE" /&gt;&lt;Set Cost="850"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2280,7 +2872,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_OXFORD_UNIVERSITY" /&gt;&lt;Set Cost="850"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>60</v>
       </c>
@@ -2296,7 +2888,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STATUE_LIBERTY" /&gt;&lt;Set Cost="850"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2312,7 +2904,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BIG_BEN" /&gt;&lt;Set Cost="1000"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>62</v>
       </c>
@@ -2328,7 +2920,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HERMITAGE" /&gt;&lt;Set Cost="1000"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -2344,7 +2936,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_EIFFEL_TOWER" /&gt;&lt;Set Cost="1280"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>64</v>
       </c>
@@ -2360,7 +2952,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BROADWAY" /&gt;&lt;Set Cost="1280"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>65</v>
       </c>
@@ -2376,7 +2968,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CRISTO_REDENTOR" /&gt;&lt;Set Cost="1280"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>66</v>
       </c>
@@ -2392,7 +2984,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AMUNDSEN_SCOTT_RESEARCH_STATION" /&gt;&lt;Set Cost="1280"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>67</v>
       </c>
@@ -2408,7 +3000,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOLDEN_GATE_BRIDGE" /&gt;&lt;Set Cost="1280"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>68</v>
       </c>
@@ -2424,7 +3016,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ESTADIO_DO_MARACANA" /&gt;&lt;Set Cost="1365"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -2440,7 +3032,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BIOSPHERE" /&gt;&lt;Set Cost="1365"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>70</v>
       </c>
@@ -2457,28 +3049,29 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B53">
+  <sortState ref="A1:B53">
     <sortCondition ref="B53"/>
   </sortState>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:T145"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.6640625" customWidth="1"/>
+    <col min="1" max="1" width="30.6666666666667" customWidth="1"/>
     <col min="6" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="75.77734375" customWidth="1"/>
+    <col min="9" max="9" width="75.775" customWidth="1"/>
     <col min="11" max="11" width="29" customWidth="1"/>
-    <col min="14" max="14" width="28.44140625" customWidth="1"/>
-    <col min="20" max="20" width="75.77734375" customWidth="1"/>
+    <col min="14" max="14" width="28.4416666666667" customWidth="1"/>
+    <col min="20" max="20" width="75.775" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20">
       <c r="D1">
         <v>0.78</v>
       </c>
@@ -2486,7 +3079,7 @@
         <v>0.87</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G1" t="s">
         <v>2</v>
@@ -2495,13 +3088,13 @@
         <v>3</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>295</v>
+        <v>72</v>
       </c>
       <c r="P1">
-        <v>1.2050000000000001</v>
+        <v>1.205</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="R1" t="s">
         <v>2</v>
@@ -2510,9 +3103,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -2529,7 +3122,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -2542,7 +3135,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SCOUT" /&gt;&lt;Set Cost="25"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L2">
         <v>60</v>
@@ -2551,7 +3144,7 @@
         <v>14</v>
       </c>
       <c r="N2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O2">
         <v>40</v>
@@ -2561,7 +3154,7 @@
         <v>50</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R2" t="s">
         <v>2</v>
@@ -2574,9 +3167,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MONUMENT" /&gt;&lt;Set Cost="50"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <v>35</v>
@@ -2593,7 +3186,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G3" t="s">
         <v>2</v>
@@ -2606,7 +3199,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SLINGER" /&gt;&lt;Set Cost="30"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L3">
         <v>65</v>
@@ -2615,7 +3208,7 @@
         <v>14</v>
       </c>
       <c r="N3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O3">
         <v>50</v>
@@ -2625,7 +3218,7 @@
         <v>60</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R3" t="s">
         <v>2</v>
@@ -2638,9 +3231,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GRANARY" /&gt;&lt;Set Cost="60"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>35</v>
@@ -2657,7 +3250,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
         <v>2</v>
@@ -2670,7 +3263,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BARBARIAN_HORSE_ARCHER" /&gt;&lt;Set Cost="30"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L4">
         <v>70</v>
@@ -2679,7 +3272,7 @@
         <v>14</v>
       </c>
       <c r="N4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="O4">
         <v>55</v>
@@ -2689,7 +3282,7 @@
         <v>65</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R4" t="s">
         <v>2</v>
@@ -2702,9 +3295,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SHRINE" /&gt;&lt;Set Cost="65"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5">
         <v>35</v>
@@ -2721,7 +3314,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
         <v>2</v>
@@ -2734,7 +3327,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BABYLONIAN_SABUM_KIBITTUM" /&gt;&lt;Set Cost="30"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L5">
         <v>80</v>
@@ -2743,7 +3336,7 @@
         <v>14</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="O5">
         <v>60</v>
@@ -2753,7 +3346,7 @@
         <v>70</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R5" t="s">
         <v>2</v>
@@ -2766,7 +3359,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WALLS" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" t="s">
         <v>81</v>
       </c>
@@ -2785,7 +3378,7 @@
         <v>35</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
         <v>2</v>
@@ -2798,7 +3391,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_WARRIOR" /&gt;&lt;Set Cost="35"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L6">
         <v>80</v>
@@ -2807,7 +3400,7 @@
         <v>14</v>
       </c>
       <c r="N6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O6">
         <v>60</v>
@@ -2817,7 +3410,7 @@
         <v>70</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R6" t="s">
         <v>2</v>
@@ -2830,7 +3423,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WATER_MILL" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2849,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G7" t="s">
         <v>2</v>
@@ -2862,7 +3455,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BARBARIAN_HORSEMAN" /&gt;&lt;Set Cost="35"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="L7">
         <v>80</v>
@@ -2871,7 +3464,7 @@
         <v>14</v>
       </c>
       <c r="N7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O7">
         <v>60</v>
@@ -2881,7 +3474,7 @@
         <v>70</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R7" t="s">
         <v>2</v>
@@ -2894,7 +3487,7 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FLOOD_BARRIER" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -2913,7 +3506,7 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G8" t="s">
         <v>2</v>
@@ -2926,7 +3519,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CREE_OKIHTCITAW" /&gt;&lt;Set Cost="35"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L8">
         <v>80</v>
@@ -2935,7 +3528,7 @@
         <v>14</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O8">
         <v>60</v>
@@ -2945,7 +3538,7 @@
         <v>70</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
         <v>2</v>
@@ -2958,9 +3551,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PALGUM" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B9">
         <v>55</v>
@@ -2977,7 +3570,7 @@
         <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G9" t="s">
         <v>2</v>
@@ -2990,7 +3583,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SUMERIAN_WAR_CART" /&gt;&lt;Set Cost="50"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L9">
         <v>90</v>
@@ -2999,7 +3592,7 @@
         <v>14</v>
       </c>
       <c r="N9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O9">
         <v>70</v>
@@ -3009,7 +3602,7 @@
         <v>85</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
         <v>2</v>
@@ -3022,9 +3615,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BARRACKS" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B10">
         <v>60</v>
@@ -3041,7 +3634,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G10" t="s">
         <v>2</v>
@@ -3054,7 +3647,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ARCHER" /&gt;&lt;Set Cost="50"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L10">
         <v>90</v>
@@ -3063,7 +3656,7 @@
         <v>14</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O10">
         <v>70</v>
@@ -3073,7 +3666,7 @@
         <v>85</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R10" t="s">
         <v>2</v>
@@ -3086,9 +3679,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_LIBRARY" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11">
         <v>60</v>
@@ -3105,7 +3698,7 @@
         <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G11" t="s">
         <v>2</v>
@@ -3118,7 +3711,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MAYAN_HULCHE" /&gt;&lt;Set Cost="50"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="L11">
         <v>90</v>
@@ -3127,7 +3720,7 @@
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O11">
         <v>70</v>
@@ -3137,7 +3730,7 @@
         <v>85</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R11" t="s">
         <v>2</v>
@@ -3150,9 +3743,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BASILIKOI_PAIDES" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B12">
         <v>60</v>
@@ -3169,7 +3762,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
         <v>2</v>
@@ -3182,7 +3775,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_GAUL_GAESATAE" /&gt;&lt;Set Cost="50"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L12">
         <v>120</v>
@@ -3191,7 +3784,7 @@
         <v>16</v>
       </c>
       <c r="N12" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="O12">
         <v>90</v>
@@ -3201,7 +3794,7 @@
         <v>110</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R12" t="s">
         <v>2</v>
@@ -3214,9 +3807,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GROVE" /&gt;&lt;Set Cost="110"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13">
         <v>65</v>
@@ -3233,7 +3826,7 @@
         <v>55</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G13" t="s">
         <v>2</v>
@@ -3246,7 +3839,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_GALLEY" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L13">
         <v>120</v>
@@ -3255,7 +3848,7 @@
         <v>16</v>
       </c>
       <c r="N13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -3265,7 +3858,7 @@
         <v>120</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R13" t="s">
         <v>2</v>
@@ -3278,9 +3871,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_LIGHTHOUSE" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14">
         <v>65</v>
@@ -3297,7 +3890,7 @@
         <v>55</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G14" t="s">
         <v>2</v>
@@ -3310,7 +3903,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_NORWEGIAN_LONGSHIP" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L14">
         <v>120</v>
@@ -3319,7 +3912,7 @@
         <v>16</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="O14">
         <v>100</v>
@@ -3329,7 +3922,7 @@
         <v>120</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R14" t="s">
         <v>2</v>
@@ -3342,9 +3935,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MARKET" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B15">
         <v>65</v>
@@ -3361,7 +3954,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G15" t="s">
         <v>2</v>
@@ -3374,7 +3967,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SPEARMAN" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K15" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="L15">
         <v>120</v>
@@ -3383,7 +3976,7 @@
         <v>16</v>
       </c>
       <c r="N15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3393,7 +3986,7 @@
         <v>120</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R15" t="s">
         <v>2</v>
@@ -3406,9 +3999,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STABLE" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16">
         <v>65</v>
@@ -3425,7 +4018,7 @@
         <v>55</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
         <v>2</v>
@@ -3438,7 +4031,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_HEAVY_CHARIOT" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L16">
         <v>120</v>
@@ -3447,7 +4040,7 @@
         <v>16</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3457,7 +4050,7 @@
         <v>120</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R16" t="s">
         <v>2</v>
@@ -3470,9 +4063,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TEMPLE" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>65</v>
@@ -3489,7 +4082,7 @@
         <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G17" t="s">
         <v>2</v>
@@ -3502,7 +4095,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BATTERING_RAM" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K17" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L17">
         <v>120</v>
@@ -3511,7 +4104,7 @@
         <v>16</v>
       </c>
       <c r="N17" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -3521,7 +4114,7 @@
         <v>120</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R17" t="s">
         <v>2</v>
@@ -3534,9 +4127,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STAVE_CHURCH" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B18">
         <v>65</v>
@@ -3553,7 +4146,7 @@
         <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
         <v>2</v>
@@ -3566,7 +4159,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_GREEK_HOPLITE" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K18" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="L18">
         <v>120</v>
@@ -3575,17 +4168,17 @@
         <v>16</v>
       </c>
       <c r="N18" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <f t="shared" si="0"/>
+        <f>ROUND(O18*P$1/5,0)*5</f>
         <v>120</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R18" t="s">
         <v>2</v>
@@ -3594,13 +4187,13 @@
         <v>3</v>
       </c>
       <c r="T18" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SEWER" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q18,N18,R18,P18,S18)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PRASAT" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B19">
         <v>65</v>
@@ -3617,7 +4210,7 @@
         <v>55</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G19" t="s">
         <v>2</v>
@@ -3630,7 +4223,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_AZTEC_EAGLE_WARRIOR" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L19">
         <v>120</v>
@@ -3639,17 +4232,17 @@
         <v>16</v>
       </c>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <f t="shared" si="0"/>
+        <f>ROUND(O19*P$1/5,0)*5</f>
         <v>120</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R19" t="s">
         <v>2</v>
@@ -3658,13 +4251,13 @@
         <v>3</v>
       </c>
       <c r="T19" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PRASAT" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q19,N19,R19,P19,S19)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SUKIENNICE" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B20">
         <v>65</v>
@@ -3681,7 +4274,7 @@
         <v>55</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G20" t="s">
         <v>2</v>
@@ -3694,7 +4287,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PHOENICIA_BIREME" /&gt;&lt;Set Cost="55"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L20">
         <v>135</v>
@@ -3703,17 +4296,17 @@
         <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="O20">
         <v>100</v>
       </c>
       <c r="P20">
-        <f t="shared" si="0"/>
+        <f>ROUND(O20*P$1/5,0)*5</f>
         <v>120</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R20" t="s">
         <v>2</v>
@@ -3722,13 +4315,13 @@
         <v>3</v>
       </c>
       <c r="T20" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SUKIENNICE" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q20,N20,R20,P20,S20)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ORDU" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21">
         <v>70</v>
@@ -3745,7 +4338,7 @@
         <v>60</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G21" t="s">
         <v>2</v>
@@ -3758,7 +4351,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_NUBIAN_PITATI" /&gt;&lt;Set Cost="60"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K21" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="L21">
         <v>150</v>
@@ -3767,17 +4360,17 @@
         <v>16</v>
       </c>
       <c r="N21" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="P21">
-        <f t="shared" si="0"/>
-        <v>120</v>
+        <f>ROUND(O21*P$1/5,0)*5</f>
+        <v>125</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R21" t="s">
         <v>2</v>
@@ -3786,13 +4379,13 @@
         <v>3</v>
       </c>
       <c r="T21" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ORDU" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q21,N21,R21,P21,S21)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TLACHTLI" /&gt;&lt;Set Cost="125"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="B22">
         <v>80</v>
@@ -3809,7 +4402,7 @@
         <v>70</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G22" t="s">
         <v>2</v>
@@ -3822,7 +4415,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_HORSEMAN" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K22" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="L22">
         <v>150</v>
@@ -3831,17 +4424,17 @@
         <v>16</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="O22">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P22">
-        <f t="shared" si="0"/>
-        <v>125</v>
+        <f>ROUND(O22*P$1/5,0)*5</f>
+        <v>135</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R22" t="s">
         <v>2</v>
@@ -3850,13 +4443,13 @@
         <v>3</v>
       </c>
       <c r="T22" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TLACHTLI" /&gt;&lt;Set Cost="125"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q22,N22,R22,P22,S22)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ARENA" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B23">
         <v>90</v>
@@ -3873,7 +4466,7 @@
         <v>80</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G23" t="s">
         <v>2</v>
@@ -3886,7 +4479,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SWORDSMAN" /&gt;&lt;Set Cost="80"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K23" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L23">
         <v>150</v>
@@ -3895,17 +4488,17 @@
         <v>16</v>
       </c>
       <c r="N23" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="O23">
         <v>110</v>
       </c>
       <c r="P23">
-        <f t="shared" si="0"/>
+        <f>ROUND(O23*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R23" t="s">
         <v>2</v>
@@ -3914,13 +4507,13 @@
         <v>3</v>
       </c>
       <c r="T23" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ARENA" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q23,N23,R23,P23,S23)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AMPHITHEATER" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B24">
         <v>90</v>
@@ -3937,7 +4530,7 @@
         <v>80</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G24" t="s">
         <v>2</v>
@@ -3950,7 +4543,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_EGYPTIAN_CHARIOT_ARCHER" /&gt;&lt;Set Cost="80"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K24" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L24">
         <v>150</v>
@@ -3959,17 +4552,17 @@
         <v>16</v>
       </c>
       <c r="N24" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="O24">
         <v>110</v>
       </c>
       <c r="P24">
-        <f t="shared" si="0"/>
+        <f>ROUND(O24*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R24" t="s">
         <v>2</v>
@@ -3978,13 +4571,13 @@
         <v>3</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AMPHITHEATER" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q24,N24,R24,P24,S24)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_TALL" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B25">
         <v>100</v>
@@ -4001,7 +4594,7 @@
         <v>85</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G25" t="s">
         <v>2</v>
@@ -4014,7 +4607,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_WARRIOR_MONK" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="L25">
         <v>150</v>
@@ -4023,17 +4616,17 @@
         <v>16</v>
       </c>
       <c r="N25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="O25">
         <v>110</v>
       </c>
       <c r="P25">
-        <f t="shared" si="0"/>
+        <f>ROUND(O25*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R25" t="s">
         <v>2</v>
@@ -4042,13 +4635,13 @@
         <v>3</v>
       </c>
       <c r="T25" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_TALL" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q25,N25,R25,P25,S25)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_WIDE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B26">
         <v>100</v>
@@ -4065,7 +4658,7 @@
         <v>85</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G26" t="s">
         <v>2</v>
@@ -4078,7 +4671,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SCYTHIAN_HORSE_ARCHER" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K26" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="L26">
         <v>150</v>
@@ -4087,17 +4680,17 @@
         <v>16</v>
       </c>
       <c r="N26" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="O26">
         <v>110</v>
       </c>
       <c r="P26">
-        <f t="shared" si="0"/>
+        <f>ROUND(O26*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R26" t="s">
         <v>2</v>
@@ -4106,13 +4699,13 @@
         <v>3</v>
       </c>
       <c r="T26" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_WIDE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q26,N26,R26,P26,S26)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CONQUEST" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B27">
         <v>100</v>
@@ -4129,7 +4722,7 @@
         <v>85</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G27" t="s">
         <v>2</v>
@@ -4142,7 +4735,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SIEGE_TOWER" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K27" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L27">
         <v>150</v>
@@ -4151,17 +4744,17 @@
         <v>16</v>
       </c>
       <c r="N27" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="O27">
         <v>110</v>
       </c>
       <c r="P27">
-        <f t="shared" si="0"/>
+        <f>ROUND(O27*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R27" t="s">
         <v>2</v>
@@ -4170,13 +4763,13 @@
         <v>3</v>
       </c>
       <c r="T27" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CONQUEST" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q27,N27,R27,P27,S27)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MARAE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B28">
         <v>100</v>
@@ -4193,7 +4786,7 @@
         <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
         <v>2</v>
@@ -4206,7 +4799,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MACEDONIAN_HYPASPIST" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K28" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="L28">
         <v>150</v>
@@ -4215,17 +4808,17 @@
         <v>16</v>
       </c>
       <c r="N28" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="O28">
         <v>110</v>
       </c>
       <c r="P28">
-        <f t="shared" si="0"/>
+        <f>ROUND(O28*P$1/5,0)*5</f>
         <v>135</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R28" t="s">
         <v>2</v>
@@ -4234,13 +4827,13 @@
         <v>3</v>
       </c>
       <c r="T28" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MARAE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q28,N28,R28,P28,S28)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CONSULATE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B29">
         <v>100</v>
@@ -4257,7 +4850,7 @@
         <v>85</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G29" t="s">
         <v>2</v>
@@ -4270,7 +4863,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MACEDONIAN_HETAIROI" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K29" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L29">
         <v>150</v>
@@ -4279,17 +4872,17 @@
         <v>16</v>
       </c>
       <c r="N29" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O29">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="P29">
-        <f t="shared" si="0"/>
-        <v>135</v>
+        <f>ROUND(O29*P$1/5,0)*5</f>
+        <v>195</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R29" t="s">
         <v>2</v>
@@ -4298,13 +4891,13 @@
         <v>3</v>
       </c>
       <c r="T29" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CONSULATE" /&gt;&lt;Set Cost="135"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q29,N29,R29,P29,S29)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WORKSHOP" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B30">
         <v>100</v>
@@ -4321,7 +4914,7 @@
         <v>85</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G30" t="s">
         <v>2</v>
@@ -4334,7 +4927,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PERSIAN_IMMORTAL" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K30" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="L30">
         <v>190</v>
@@ -4343,17 +4936,17 @@
         <v>18</v>
       </c>
       <c r="N30" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="O30">
         <v>160</v>
       </c>
       <c r="P30">
-        <f t="shared" si="0"/>
+        <f>ROUND(O30*P$1/5,0)*5</f>
         <v>195</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R30" t="s">
         <v>2</v>
@@ -4362,13 +4955,13 @@
         <v>3</v>
       </c>
       <c r="T30" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WORKSHOP" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q30,N30,R30,P30,S30)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ARMORY" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B31">
         <v>100</v>
@@ -4385,7 +4978,7 @@
         <v>85</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G31" t="s">
         <v>2</v>
@@ -4398,7 +4991,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_LAHORE_NIHANG" /&gt;&lt;Set Cost="85"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K31" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L31">
         <v>190</v>
@@ -4407,17 +5000,17 @@
         <v>18</v>
       </c>
       <c r="N31" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="O31">
         <v>160</v>
       </c>
       <c r="P31">
-        <f t="shared" si="0"/>
+        <f>ROUND(O31*P$1/5,0)*5</f>
         <v>195</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R31" t="s">
         <v>2</v>
@@ -4426,13 +5019,13 @@
         <v>3</v>
       </c>
       <c r="T31" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ARMORY" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q31,N31,R31,P31,S31)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CATHEDRAL" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B32">
         <v>110</v>
@@ -4449,7 +5042,7 @@
         <v>95</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G32" t="s">
         <v>2</v>
@@ -4462,7 +5055,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ROMAN_LEGION" /&gt;&lt;Set Cost="95"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K32" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="L32">
         <v>190</v>
@@ -4471,17 +5064,17 @@
         <v>18</v>
       </c>
       <c r="N32" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="O32">
         <v>160</v>
       </c>
       <c r="P32">
-        <f t="shared" si="0"/>
+        <f>ROUND(O32*P$1/5,0)*5</f>
         <v>195</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R32" t="s">
         <v>2</v>
@@ -4490,13 +5083,13 @@
         <v>3</v>
       </c>
       <c r="T32" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CATHEDRAL" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q32,N32,R32,P32,S32)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GURDWARA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B33">
         <v>110</v>
@@ -4513,7 +5106,7 @@
         <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G33" t="s">
         <v>2</v>
@@ -4526,7 +5119,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_KONGO_SHIELD_BEARER" /&gt;&lt;Set Cost="95"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K33" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="L33">
         <v>190</v>
@@ -4535,17 +5128,17 @@
         <v>18</v>
       </c>
       <c r="N33" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="O33">
         <v>160</v>
       </c>
       <c r="P33">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="P33:P59" si="7">ROUND(O33*P$1/5,0)*5</f>
         <v>195</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R33" t="s">
         <v>2</v>
@@ -4554,13 +5147,13 @@
         <v>3</v>
       </c>
       <c r="T33" t="str">
-        <f t="shared" si="1"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GURDWARA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" ref="T33:T59" si="8">_xlfn.CONCAT(Q33,N33,R33,P33,S33)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MEETING_HOUSE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B34">
         <v>120</v>
@@ -4577,7 +5170,7 @@
         <v>105</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G34" t="s">
         <v>2</v>
@@ -4590,7 +5183,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CATAPULT" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K34" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L34">
         <v>190</v>
@@ -4599,17 +5192,17 @@
         <v>18</v>
       </c>
       <c r="N34" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="O34">
         <v>160</v>
       </c>
       <c r="P34">
-        <f t="shared" ref="P34:P65" si="7">ROUND(O34*P$1/5,0)*5</f>
+        <f t="shared" si="7"/>
         <v>195</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R34" t="s">
         <v>2</v>
@@ -4618,13 +5211,13 @@
         <v>3</v>
       </c>
       <c r="T34" t="str">
-        <f t="shared" ref="T34:T65" si="8">_xlfn.CONCAT(Q34,N34,R34,P34,S34)</f>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MEETING_HOUSE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MOSQUE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B35">
         <v>120</v>
@@ -4641,7 +5234,7 @@
         <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
         <v>2</v>
@@ -4654,7 +5247,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_QUADRIREME" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K35" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L35">
         <v>190</v>
@@ -4663,7 +5256,7 @@
         <v>18</v>
       </c>
       <c r="N35" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="O35">
         <v>160</v>
@@ -4673,7 +5266,7 @@
         <v>195</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R35" t="s">
         <v>2</v>
@@ -4683,12 +5276,12 @@
       </c>
       <c r="T35" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MOSQUE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PAGODA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="B36">
         <v>120</v>
@@ -4705,7 +5298,7 @@
         <v>105</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G36" t="s">
         <v>2</v>
@@ -4718,7 +5311,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_INDIAN_VARU" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L36">
         <v>190</v>
@@ -4727,7 +5320,7 @@
         <v>18</v>
       </c>
       <c r="N36" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="O36">
         <v>160</v>
@@ -4737,7 +5330,7 @@
         <v>195</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R36" t="s">
         <v>2</v>
@@ -4747,12 +5340,12 @@
       </c>
       <c r="T36" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PAGODA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SYNAGOGUE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B37">
         <v>120</v>
@@ -4769,7 +5362,7 @@
         <v>105</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G37" t="s">
         <v>2</v>
@@ -4782,7 +5375,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MAORI_TOA" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K37" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="L37">
         <v>190</v>
@@ -4791,7 +5384,7 @@
         <v>18</v>
       </c>
       <c r="N37" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="O37">
         <v>160</v>
@@ -4801,7 +5394,7 @@
         <v>195</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R37" t="s">
         <v>2</v>
@@ -4811,12 +5404,12 @@
       </c>
       <c r="T37" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SYNAGOGUE" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WAT" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B38">
         <v>120</v>
@@ -4833,7 +5426,7 @@
         <v>105</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G38" t="s">
         <v>2</v>
@@ -4846,7 +5439,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SULEIMAN_JANISSARY" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K38" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="L38">
         <v>190</v>
@@ -4855,7 +5448,7 @@
         <v>18</v>
       </c>
       <c r="N38" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O38">
         <v>160</v>
@@ -4865,7 +5458,7 @@
         <v>195</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R38" t="s">
         <v>2</v>
@@ -4875,12 +5468,12 @@
       </c>
       <c r="T38" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_WAT" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STUPA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B39">
         <v>120</v>
@@ -4897,7 +5490,7 @@
         <v>105</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G39" t="s">
         <v>2</v>
@@ -4910,7 +5503,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BYZANTINE_DROMON" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K39" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="L39">
         <v>195</v>
@@ -4919,7 +5512,7 @@
         <v>18</v>
       </c>
       <c r="N39" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="O39">
         <v>160</v>
@@ -4929,7 +5522,7 @@
         <v>195</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R39" t="s">
         <v>2</v>
@@ -4939,12 +5532,12 @@
       </c>
       <c r="T39" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STUPA" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_DAR_E_MEHR" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B40">
         <v>125</v>
@@ -4961,7 +5554,7 @@
         <v>110</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G40" t="s">
         <v>2</v>
@@ -4974,7 +5567,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ZULU_IMPI" /&gt;&lt;Set Cost="110"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K40" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="L40">
         <v>195</v>
@@ -4983,17 +5576,17 @@
         <v>18</v>
       </c>
       <c r="N40" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="O40">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="P40">
         <f t="shared" si="7"/>
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R40" t="s">
         <v>2</v>
@@ -5003,12 +5596,12 @@
       </c>
       <c r="T40" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_DAR_E_MEHR" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CASTLE" /&gt;&lt;Set Cost="215"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B41">
         <v>140</v>
@@ -5025,7 +5618,7 @@
         <v>120</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G41" t="s">
         <v>2</v>
@@ -5038,7 +5631,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CHINESE_CROUCHING_TIGER" /&gt;&lt;Set Cost="120"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K41" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="L41">
         <v>200</v>
@@ -5057,7 +5650,7 @@
         <v>215</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R41" t="s">
         <v>2</v>
@@ -5067,12 +5660,12 @@
       </c>
       <c r="T41" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CASTLE" /&gt;&lt;Set Cost="215"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_QUEENS_BIBLIOTHEQUE" /&gt;&lt;Set Cost="215"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B42">
         <v>150</v>
@@ -5089,7 +5682,7 @@
         <v>130</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G42" t="s">
         <v>2</v>
@@ -5102,7 +5695,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SKIRMISHER" /&gt;&lt;Set Cost="130"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K42" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="L42">
         <v>217</v>
@@ -5111,17 +5704,17 @@
         <v>18</v>
       </c>
       <c r="N42" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="O42">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="P42">
         <f t="shared" si="7"/>
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R42" t="s">
         <v>2</v>
@@ -5131,12 +5724,12 @@
       </c>
       <c r="T42" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_QUEENS_BIBLIOTHEQUE" /&gt;&lt;Set Cost="215"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GRAND_BAZAAR" /&gt;&lt;Set Cost="230"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B43">
         <v>160</v>
@@ -5153,7 +5746,7 @@
         <v>140</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G43" t="s">
         <v>2</v>
@@ -5166,7 +5759,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_JAPANESE_SAMURAI" /&gt;&lt;Set Cost="140"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K43" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="L43">
         <v>220</v>
@@ -5175,17 +5768,17 @@
         <v>18</v>
       </c>
       <c r="N43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O43">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="P43">
         <f t="shared" si="7"/>
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R43" t="s">
         <v>2</v>
@@ -5195,12 +5788,12 @@
       </c>
       <c r="T43" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GRAND_BAZAAR" /&gt;&lt;Set Cost="230"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_UNIVERSITY" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B44">
         <v>160</v>
@@ -5217,7 +5810,7 @@
         <v>140</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G44" t="s">
         <v>2</v>
@@ -5239,7 +5832,7 @@
         <v>18</v>
       </c>
       <c r="N44" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O44">
         <v>200</v>
@@ -5249,7 +5842,7 @@
         <v>240</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R44" t="s">
         <v>2</v>
@@ -5259,12 +5852,12 @@
       </c>
       <c r="T44" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_UNIVERSITY" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MADRASA" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B45">
         <v>160</v>
@@ -5281,7 +5874,7 @@
         <v>140</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G45" t="s">
         <v>2</v>
@@ -5303,7 +5896,7 @@
         <v>18</v>
       </c>
       <c r="N45" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O45">
         <v>200</v>
@@ -5313,7 +5906,7 @@
         <v>240</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R45" t="s">
         <v>2</v>
@@ -5323,12 +5916,12 @@
       </c>
       <c r="T45" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MADRASA" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TSIKHE" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="B46">
         <v>160</v>
@@ -5345,7 +5938,7 @@
         <v>140</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G46" t="s">
         <v>2</v>
@@ -5377,7 +5970,7 @@
         <v>240</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R46" t="s">
         <v>2</v>
@@ -5387,12 +5980,12 @@
       </c>
       <c r="T46" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_TSIKHE" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_NAVIGATION_SCHOOL" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B47">
         <v>160</v>
@@ -5409,7 +6002,7 @@
         <v>140</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G47" t="s">
         <v>2</v>
@@ -5422,7 +6015,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_GEORGIAN_KHEVSURETI" /&gt;&lt;Set Cost="140"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K47" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L47">
         <v>250</v>
@@ -5431,17 +6024,17 @@
         <v>18</v>
       </c>
       <c r="N47" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="O47">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="P47">
         <f t="shared" si="7"/>
-        <v>240</v>
+        <v>275</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R47" t="s">
         <v>2</v>
@@ -5451,12 +6044,12 @@
       </c>
       <c r="T47" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_NAVIGATION_SCHOOL" /&gt;&lt;Set Cost="240"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ZOO" /&gt;&lt;Set Cost="275"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B48">
         <v>165</v>
@@ -5473,7 +6066,7 @@
         <v>145</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G48" t="s">
         <v>2</v>
@@ -5486,7 +6079,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_INCA_WARAKAQ" /&gt;&lt;Set Cost="145"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="L48">
         <v>260</v>
@@ -5495,7 +6088,7 @@
         <v>18</v>
       </c>
       <c r="N48" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="O48">
         <v>230</v>
@@ -5505,7 +6098,7 @@
         <v>275</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R48" t="s">
         <v>2</v>
@@ -5515,12 +6108,12 @@
       </c>
       <c r="T48" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ZOO" /&gt;&lt;Set Cost="275"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_THERMAL_BATH" /&gt;&lt;Set Cost="275"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B49">
         <v>170</v>
@@ -5537,7 +6130,7 @@
         <v>150</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G49" t="s">
         <v>2</v>
@@ -5550,7 +6143,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MILITARY_ENGINEER" /&gt;&lt;Set Cost="150"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K49" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="L49">
         <v>290</v>
@@ -5559,17 +6152,17 @@
         <v>20</v>
       </c>
       <c r="N49" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="O49">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="P49">
         <f t="shared" si="7"/>
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R49" t="s">
         <v>2</v>
@@ -5579,12 +6172,12 @@
       </c>
       <c r="T49" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_THERMAL_BATH" /&gt;&lt;Set Cost="275"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SHIPYARD" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="B50">
         <v>180</v>
@@ -5601,7 +6194,7 @@
         <v>155</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G50" t="s">
         <v>2</v>
@@ -5614,7 +6207,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CROSSBOWMAN" /&gt;&lt;Set Cost="155"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K50" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="L50">
         <v>290</v>
@@ -5623,7 +6216,7 @@
         <v>20</v>
       </c>
       <c r="N50" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="O50">
         <v>240</v>
@@ -5633,7 +6226,7 @@
         <v>290</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R50" t="s">
         <v>2</v>
@@ -5643,12 +6236,12 @@
       </c>
       <c r="T50" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SHIPYARD" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BANK" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B51">
         <v>180</v>
@@ -5665,7 +6258,7 @@
         <v>155</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G51" t="s">
         <v>2</v>
@@ -5678,7 +6271,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PIKEMAN" /&gt;&lt;Set Cost="155"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K51" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="L51">
         <v>290</v>
@@ -5687,7 +6280,7 @@
         <v>20</v>
       </c>
       <c r="N51" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="O51">
         <v>240</v>
@@ -5697,7 +6290,7 @@
         <v>290</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R51" t="s">
         <v>2</v>
@@ -5707,12 +6300,12 @@
       </c>
       <c r="T51" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BANK" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MUSEUM_ART" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="B52">
         <v>200</v>
@@ -5729,7 +6322,7 @@
         <v>175</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G52" t="s">
         <v>2</v>
@@ -5742,7 +6335,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_TREBUCHET" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K52" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L52">
         <v>290</v>
@@ -5751,7 +6344,7 @@
         <v>20</v>
       </c>
       <c r="N52" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="O52">
         <v>240</v>
@@ -5761,7 +6354,7 @@
         <v>290</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R52" t="s">
         <v>2</v>
@@ -5771,12 +6364,12 @@
       </c>
       <c r="T52" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MUSEUM_ART" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MUSEUM_ARTIFACT" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="B53">
         <v>200</v>
@@ -5793,7 +6386,7 @@
         <v>175</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G53" t="s">
         <v>2</v>
@@ -5806,7 +6399,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_KHMER_DOMREY" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K53" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L53">
         <v>290</v>
@@ -5815,7 +6408,7 @@
         <v>20</v>
       </c>
       <c r="N53" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="O53">
         <v>240</v>
@@ -5825,7 +6418,7 @@
         <v>290</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R53" t="s">
         <v>2</v>
@@ -5835,12 +6428,12 @@
       </c>
       <c r="T53" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MUSEUM_ARTIFACT" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FERRIS_WHEEL" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B54">
         <v>200</v>
@@ -5857,7 +6450,7 @@
         <v>175</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G54" t="s">
         <v>2</v>
@@ -5870,7 +6463,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_COURSER" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K54" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="L54">
         <v>290</v>
@@ -5879,7 +6472,7 @@
         <v>20</v>
       </c>
       <c r="N54" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="O54">
         <v>240</v>
@@ -5889,7 +6482,7 @@
         <v>290</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R54" t="s">
         <v>2</v>
@@ -5899,12 +6492,12 @@
       </c>
       <c r="T54" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FERRIS_WHEEL" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CITYSTATES" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B55">
         <v>200</v>
@@ -5921,7 +6514,7 @@
         <v>175</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G55" t="s">
         <v>2</v>
@@ -5934,7 +6527,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_VIETNAMESE_VOI_CHIEN" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K55" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="L55">
         <v>290</v>
@@ -5943,7 +6536,7 @@
         <v>20</v>
       </c>
       <c r="N55" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="O55">
         <v>240</v>
@@ -5953,7 +6546,7 @@
         <v>290</v>
       </c>
       <c r="Q55" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R55" t="s">
         <v>2</v>
@@ -5963,12 +6556,12 @@
       </c>
       <c r="T55" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CITYSTATES" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_SPIES" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="B56">
         <v>200</v>
@@ -5985,7 +6578,7 @@
         <v>175</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G56" t="s">
         <v>2</v>
@@ -5998,7 +6591,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ETHIOPIAN_OROMO_CAVALRY" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K56" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="L56">
         <v>290</v>
@@ -6007,7 +6600,7 @@
         <v>20</v>
       </c>
       <c r="N56" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="O56">
         <v>240</v>
@@ -6017,7 +6610,7 @@
         <v>290</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R56" t="s">
         <v>2</v>
@@ -6027,12 +6620,12 @@
       </c>
       <c r="T56" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_SPIES" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_FAITH" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B57">
         <v>205</v>
@@ -6049,7 +6642,7 @@
         <v>180</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G57" t="s">
         <v>2</v>
@@ -6062,7 +6655,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_HUNGARY_BLACK_ARMY" /&gt;&lt;Set Cost="180"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K57" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="L57">
         <v>290</v>
@@ -6071,7 +6664,7 @@
         <v>20</v>
       </c>
       <c r="N57" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="O57">
         <v>240</v>
@@ -6081,7 +6674,7 @@
         <v>290</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R57" t="s">
         <v>2</v>
@@ -6091,12 +6684,12 @@
       </c>
       <c r="T57" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_FAITH" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CHANCERY" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B58">
         <v>220</v>
@@ -6113,7 +6706,7 @@
         <v>190</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G58" t="s">
         <v>2</v>
@@ -6126,7 +6719,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_KNIGHT" /&gt;&lt;Set Cost="190"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K58" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L58">
         <v>300</v>
@@ -6135,17 +6728,17 @@
         <v>20</v>
       </c>
       <c r="N58" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O58">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="P58">
         <f t="shared" si="7"/>
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R58" t="s">
         <v>2</v>
@@ -6155,12 +6748,12 @@
       </c>
       <c r="T58" t="str">
         <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_CHANCERY" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STAR_FORT" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B59">
         <v>220</v>
@@ -6177,7 +6770,7 @@
         <v>190</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G59" t="s">
         <v>2</v>
@@ -6190,7 +6783,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ARABIAN_MAMLUK" /&gt;&lt;Set Cost="190"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K59" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="L59">
         <v>300</v>
@@ -6199,17 +6792,17 @@
         <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="O59">
-        <v>250</v>
+        <v>165</v>
       </c>
       <c r="P59">
-        <f t="shared" si="7"/>
-        <v>300</v>
+        <f>ROUND(O59*P$1/5,0)*5</f>
+        <v>200</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R59" t="s">
         <v>2</v>
@@ -6218,13 +6811,13 @@
         <v>3</v>
       </c>
       <c r="T59" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STAR_FORT" /&gt;&lt;Set Cost="300"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q59,N59,R59,P59,S59)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SEWER" /&gt;&lt;Set Cost="200"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="B60">
         <v>220</v>
@@ -6241,7 +6834,7 @@
         <v>190</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G60" t="s">
         <v>2</v>
@@ -6254,7 +6847,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MALI_MANDEKALU_CAVALRY" /&gt;&lt;Set Cost="190"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K60" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L60">
         <v>330</v>
@@ -6263,17 +6856,17 @@
         <v>22</v>
       </c>
       <c r="N60" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="O60">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="P60">
-        <f t="shared" si="7"/>
-        <v>360</v>
+        <f>ROUND(O60*P$1/5,0)*5</f>
+        <v>400</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R60" t="s">
         <v>2</v>
@@ -6282,13 +6875,13 @@
         <v>3</v>
       </c>
       <c r="T60" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FOOD_MARKET" /&gt;&lt;Set Cost="360"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q60,N60,R60,P60,S60)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FACTORY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="B61">
         <v>220</v>
@@ -6305,7 +6898,7 @@
         <v>190</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G61" t="s">
         <v>2</v>
@@ -6318,7 +6911,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BYZANTINE_TAGMA" /&gt;&lt;Set Cost="190"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K61" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L61">
         <v>330</v>
@@ -6327,17 +6920,17 @@
         <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="O61">
         <v>330</v>
       </c>
       <c r="P61">
-        <f t="shared" si="7"/>
+        <f>ROUND(O61*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R61" t="s">
         <v>2</v>
@@ -6346,13 +6939,13 @@
         <v>3</v>
       </c>
       <c r="T61" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FACTORY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q61,N61,R61,P61,S61)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ELECTRONICS_FACTORY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B62">
         <v>225</v>
@@ -6369,7 +6962,7 @@
         <v>195</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G62" t="s">
         <v>2</v>
@@ -6382,7 +6975,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SPY" /&gt;&lt;Set Cost="195"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K62" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L62">
         <v>330</v>
@@ -6391,17 +6984,17 @@
         <v>22</v>
       </c>
       <c r="N62" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="O62">
         <v>330</v>
       </c>
       <c r="P62">
-        <f t="shared" si="7"/>
+        <f>ROUND(O62*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R62" t="s">
         <v>2</v>
@@ -6410,13 +7003,13 @@
         <v>3</v>
       </c>
       <c r="T62" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_ELECTRONICS_FACTORY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q62,N62,R62,P62,S62)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STOCK_EXCHANGE" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B63">
         <v>230</v>
@@ -6433,7 +7026,7 @@
         <v>200</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G63" t="s">
         <v>2</v>
@@ -6446,7 +7039,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MAPUCHE_MALON_RAIDER" /&gt;&lt;Set Cost="200"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K63" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="L63">
         <v>330</v>
@@ -6455,17 +7048,17 @@
         <v>22</v>
       </c>
       <c r="N63" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="O63">
         <v>330</v>
       </c>
       <c r="P63">
-        <f t="shared" si="7"/>
+        <f>ROUND(O63*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R63" t="s">
         <v>2</v>
@@ -6474,13 +7067,13 @@
         <v>3</v>
       </c>
       <c r="T63" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STOCK_EXCHANGE" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q63,N63,R63,P63,S63)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MILITARY_ACADEMY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B64">
         <v>240</v>
@@ -6497,7 +7090,7 @@
         <v>210</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G64" t="s">
         <v>2</v>
@@ -6510,7 +7103,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MUSKETMAN" /&gt;&lt;Set Cost="210"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K64" t="s">
-        <v>196</v>
+        <v>166</v>
       </c>
       <c r="L64">
         <v>360</v>
@@ -6519,17 +7112,17 @@
         <v>22</v>
       </c>
       <c r="N64" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="O64">
         <v>330</v>
       </c>
       <c r="P64">
-        <f t="shared" si="7"/>
+        <f>ROUND(O64*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R64" t="s">
         <v>2</v>
@@ -6538,13 +7131,13 @@
         <v>3</v>
       </c>
       <c r="T64" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MILITARY_ACADEMY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q64,N64,R64,P64,S64)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_COAL_POWER_PLANT" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="B65">
         <v>240</v>
@@ -6561,7 +7154,7 @@
         <v>210</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G65" t="s">
         <v>2</v>
@@ -6574,7 +7167,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CARAVEL" /&gt;&lt;Set Cost="210"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K65" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="L65">
         <v>360</v>
@@ -6583,17 +7176,17 @@
         <v>22</v>
       </c>
       <c r="N65" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="O65">
         <v>330</v>
       </c>
       <c r="P65">
-        <f t="shared" si="7"/>
+        <f>ROUND(O65*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R65" t="s">
         <v>2</v>
@@ -6602,13 +7195,13 @@
         <v>3</v>
       </c>
       <c r="T65" t="str">
-        <f t="shared" si="8"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_COAL_POWER_PLANT" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q65,N65,R65,P65,S65)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SANCTUARY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B66">
         <v>240</v>
@@ -6625,7 +7218,7 @@
         <v>210</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G66" t="s">
         <v>2</v>
@@ -6638,7 +7231,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_OBSERVATION_BALLOON" /&gt;&lt;Set Cost="210"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K66" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L66">
         <v>360</v>
@@ -6647,17 +7240,17 @@
         <v>18</v>
       </c>
       <c r="N66" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="O66">
         <v>330</v>
       </c>
       <c r="P66">
-        <f t="shared" ref="P66:P87" si="12">ROUND(O66*P$1/5,0)*5</f>
+        <f>ROUND(O66*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R66" t="s">
         <v>2</v>
@@ -6666,13 +7259,13 @@
         <v>3</v>
       </c>
       <c r="T66" t="str">
-        <f t="shared" ref="T66:T87" si="13">_xlfn.CONCAT(Q66,N66,R66,P66,S66)</f>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SANCTUARY" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q66,N66,R66,P66,S66)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_OPERA_HOUSE" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B67">
         <v>240</v>
@@ -6689,7 +7282,7 @@
         <v>210</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G67" t="s">
         <v>2</v>
@@ -6702,7 +7295,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_OTTOMAN_BARBARY_CORSAIR" /&gt;&lt;Set Cost="210"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K67" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="L67">
         <v>360</v>
@@ -6711,17 +7304,17 @@
         <v>18</v>
       </c>
       <c r="N67" t="s">
-        <v>287</v>
+        <v>207</v>
       </c>
       <c r="O67">
         <v>330</v>
       </c>
       <c r="P67">
-        <f t="shared" si="12"/>
+        <f>ROUND(O67*P$1/5,0)*5</f>
         <v>400</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R67" t="s">
         <v>2</v>
@@ -6730,13 +7323,13 @@
         <v>3</v>
       </c>
       <c r="T67" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HOSPITAL" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q67,N67,R67,P67,S67)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PUBLIC_SCHOOL" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="B68">
         <v>240</v>
@@ -6753,7 +7346,7 @@
         <v>210</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G68" t="s">
         <v>2</v>
@@ -6766,7 +7359,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PORTUGUESE_NAU" /&gt;&lt;Set Cost="210"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K68" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="L68">
         <v>380</v>
@@ -6775,17 +7368,17 @@
         <v>18</v>
       </c>
       <c r="N68" t="s">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="O68">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="P68">
-        <f t="shared" si="12"/>
-        <v>400</v>
+        <f>ROUND(O68*P$1/5,0)*5</f>
+        <v>420</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R68" t="s">
         <v>2</v>
@@ -6794,13 +7387,13 @@
         <v>3</v>
       </c>
       <c r="T68" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_OPERA_HOUSE" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q68,N68,R68,P68,S68)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AQUARIUM" /&gt;&lt;Set Cost="420"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B69">
         <v>250</v>
@@ -6817,7 +7410,7 @@
         <v>220</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G69" t="s">
         <v>2</v>
@@ -6830,7 +7423,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SPANISH_CONQUISTADOR" /&gt;&lt;Set Cost="220"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K69" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="L69">
         <v>380</v>
@@ -6839,17 +7432,17 @@
         <v>18</v>
       </c>
       <c r="N69" t="s">
-        <v>289</v>
+        <v>209</v>
       </c>
       <c r="O69">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="P69">
-        <f t="shared" si="12"/>
-        <v>400</v>
+        <f>ROUND(O69*P$1/5,0)*5</f>
+        <v>445</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R69" t="s">
         <v>2</v>
@@ -6858,13 +7451,13 @@
         <v>3</v>
       </c>
       <c r="T69" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_PUBLIC_SCHOOL" /&gt;&lt;Set Cost="400"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q69,N69,R69,P69,S69)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HANGAR" /&gt;&lt;Set Cost="445"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="B70">
         <v>250</v>
@@ -6881,7 +7474,7 @@
         <v>220</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G70" t="s">
         <v>2</v>
@@ -6894,7 +7487,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_KOREAN_HWACHA" /&gt;&lt;Set Cost="220"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K70" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="L70">
         <v>440</v>
@@ -6903,17 +7496,17 @@
         <v>18</v>
       </c>
       <c r="N70" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="O70">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="P70">
-        <f t="shared" si="12"/>
-        <v>420</v>
+        <f>ROUND(O70*P$1/5,0)*5</f>
+        <v>445</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R70" t="s">
         <v>2</v>
@@ -6922,13 +7515,13 @@
         <v>3</v>
       </c>
       <c r="T70" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AQUARIUM" /&gt;&lt;Set Cost="420"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q70,N70,R70,P70,S70)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FOOD_MARKET" /&gt;&lt;Set Cost="445"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B71">
         <v>250</v>
@@ -6945,7 +7538,7 @@
         <v>220</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G71" t="s">
         <v>2</v>
@@ -6958,7 +7551,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PIKE_AND_SHOT" /&gt;&lt;Set Cost="220"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K71" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="L71">
         <v>440</v>
@@ -6967,17 +7560,17 @@
         <v>18</v>
       </c>
       <c r="N71" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="O71">
-        <v>370</v>
+        <v>430</v>
       </c>
       <c r="P71">
-        <f t="shared" si="12"/>
-        <v>445</v>
+        <f>ROUND(O71*P$1/5,0)*5</f>
+        <v>520</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R71" t="s">
         <v>2</v>
@@ -6986,13 +7579,13 @@
         <v>3</v>
       </c>
       <c r="T71" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HANGAR" /&gt;&lt;Set Cost="445"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q71,N71,R71,P71,S71)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SEAPORT" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B72">
         <v>250</v>
@@ -7009,7 +7602,7 @@
         <v>220</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G72" t="s">
         <v>2</v>
@@ -7022,7 +7615,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SWEDEN_CAROLEAN" /&gt;&lt;Set Cost="220"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K72" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="L72">
         <v>440</v>
@@ -7031,17 +7624,17 @@
         <v>18</v>
       </c>
       <c r="N72" t="s">
-        <v>290</v>
+        <v>213</v>
       </c>
       <c r="O72">
         <v>430</v>
       </c>
       <c r="P72">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="P67:P86" si="12">ROUND(O72*P$1/5,0)*5</f>
         <v>520</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R72" t="s">
         <v>2</v>
@@ -7050,13 +7643,13 @@
         <v>3</v>
       </c>
       <c r="T72" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SEAPORT" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+        <f t="shared" ref="T67:T86" si="13">_xlfn.CONCAT(Q72,N72,R72,P72,S72)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BROADCAST_CENTER" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="B73">
         <v>280</v>
@@ -7073,7 +7666,7 @@
         <v>245</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G73" t="s">
         <v>2</v>
@@ -7086,7 +7679,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BOMBARD" /&gt;&lt;Set Cost="245"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K73" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="L73">
         <v>440</v>
@@ -7095,7 +7688,7 @@
         <v>18</v>
       </c>
       <c r="N73" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="O73">
         <v>430</v>
@@ -7105,7 +7698,7 @@
         <v>520</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R73" t="s">
         <v>2</v>
@@ -7115,12 +7708,12 @@
       </c>
       <c r="T73" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_BROADCAST_CENTER" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FILM_STUDIO" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B74">
         <v>280</v>
@@ -7137,7 +7730,7 @@
         <v>245</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G74" t="s">
         <v>2</v>
@@ -7150,7 +7743,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_FRIGATE" /&gt;&lt;Set Cost="245"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K74" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L74">
         <v>440</v>
@@ -7159,7 +7752,7 @@
         <v>18</v>
       </c>
       <c r="N74" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O74">
         <v>430</v>
@@ -7169,7 +7762,7 @@
         <v>520</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R74" t="s">
         <v>2</v>
@@ -7179,12 +7772,12 @@
       </c>
       <c r="T74" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FILM_STUDIO" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_MILITARY" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B75">
         <v>280</v>
@@ -7201,7 +7794,7 @@
         <v>245</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G75" t="s">
         <v>2</v>
@@ -7214,7 +7807,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_PRIVATEER" /&gt;&lt;Set Cost="245"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K75" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="L75">
         <v>440</v>
@@ -7223,7 +7816,7 @@
         <v>18</v>
       </c>
       <c r="N75" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="O75">
         <v>430</v>
@@ -7233,7 +7826,7 @@
         <v>520</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R75" t="s">
         <v>2</v>
@@ -7243,12 +7836,12 @@
       </c>
       <c r="T75" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_MILITARY" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CULTURE" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B76">
         <v>280</v>
@@ -7265,7 +7858,7 @@
         <v>245</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G76" t="s">
         <v>2</v>
@@ -7278,7 +7871,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ENGLISH_SEADOG" /&gt;&lt;Set Cost="245"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K76" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="L76">
         <v>440</v>
@@ -7287,7 +7880,7 @@
         <v>26</v>
       </c>
       <c r="N76" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="O76">
         <v>430</v>
@@ -7297,7 +7890,7 @@
         <v>520</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R76" t="s">
         <v>2</v>
@@ -7307,12 +7900,12 @@
       </c>
       <c r="T76" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_CULTURE" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_SCIENCE" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B77">
         <v>280</v>
@@ -7329,7 +7922,7 @@
         <v>245</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G77" t="s">
         <v>2</v>
@@ -7342,7 +7935,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_DE_ZEVEN_PROVINCIEN" /&gt;&lt;Set Cost="245"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K77" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="L77">
         <v>440</v>
@@ -7351,7 +7944,7 @@
         <v>26</v>
       </c>
       <c r="N77" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="O77">
         <v>430</v>
@@ -7361,7 +7954,7 @@
         <v>520</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R77" t="s">
         <v>2</v>
@@ -7371,12 +7964,12 @@
       </c>
       <c r="T77" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_GOV_SCIENCE" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SHOPPING_MALL" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B78">
         <v>290</v>
@@ -7393,7 +7986,7 @@
         <v>250</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G78" t="s">
         <v>2</v>
@@ -7406,7 +7999,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CANADA_MOUNTIE" /&gt;&lt;Set Cost="250"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K78" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="L78">
         <v>440</v>
@@ -7415,7 +8008,7 @@
         <v>26</v>
       </c>
       <c r="N78" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O78">
         <v>430</v>
@@ -7425,7 +8018,7 @@
         <v>520</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R78" t="s">
         <v>2</v>
@@ -7435,12 +8028,12 @@
       </c>
       <c r="T78" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_SHOPPING_MALL" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HYDROELECTRIC_DAM" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="B79">
         <v>300</v>
@@ -7457,7 +8050,7 @@
         <v>260</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G79" t="s">
         <v>2</v>
@@ -7470,7 +8063,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_INDONESIAN_JONG" /&gt;&lt;Set Cost="260"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K79" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="L79">
         <v>480</v>
@@ -7479,7 +8072,7 @@
         <v>26</v>
       </c>
       <c r="N79" t="s">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="O79">
         <v>430</v>
@@ -7489,7 +8082,7 @@
         <v>520</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R79" t="s">
         <v>2</v>
@@ -7499,12 +8092,12 @@
       </c>
       <c r="T79" t="str">
         <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_HYDROELECTRIC_DAM" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FOSSIL_FUEL_POWER_PLANT" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B80">
         <v>330</v>
@@ -7521,7 +8114,7 @@
         <v>285</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G80" t="s">
         <v>2</v>
@@ -7534,7 +8127,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_FIELD_CANNON" /&gt;&lt;Set Cost="285"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K80" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="L80">
         <v>480</v>
@@ -7543,17 +8136,17 @@
         <v>26</v>
       </c>
       <c r="N80" t="s">
-        <v>200</v>
+        <v>234</v>
       </c>
       <c r="O80">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="P80">
-        <f t="shared" si="12"/>
-        <v>520</v>
+        <f>ROUND(O80*P$1/5,0)*5</f>
+        <v>540</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R80" t="s">
         <v>2</v>
@@ -7562,13 +8155,13 @@
         <v>3</v>
       </c>
       <c r="T80" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_FOSSIL_FUEL_POWER_PLANT" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q80,N80,R80,P80,S80)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STADIUM" /&gt;&lt;Set Cost="540"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B81">
         <v>330</v>
@@ -7585,7 +8178,7 @@
         <v>285</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G81" t="s">
         <v>2</v>
@@ -7598,7 +8191,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CAVALRY" /&gt;&lt;Set Cost="285"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K81" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="L81">
         <v>480</v>
@@ -7607,17 +8200,17 @@
         <v>26</v>
       </c>
       <c r="N81" t="s">
-        <v>291</v>
+        <v>231</v>
       </c>
       <c r="O81">
-        <v>430</v>
+        <v>540</v>
       </c>
       <c r="P81">
-        <f t="shared" si="12"/>
-        <v>520</v>
+        <f>ROUND(O81*P$1/5,0)*5</f>
+        <v>650</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R81" t="s">
         <v>2</v>
@@ -7626,13 +8219,13 @@
         <v>3</v>
       </c>
       <c r="T81" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MEDICAL_LAB" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q81,N81,R81,P81,S81)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_POWER_PLANT" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B82">
         <v>330</v>
@@ -7649,7 +8242,7 @@
         <v>285</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G82" t="s">
         <v>2</v>
@@ -7662,7 +8255,7 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_POLISH_HUSSAR" /&gt;&lt;Set Cost="285"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="K82" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="L82">
         <v>480</v>
@@ -7671,17 +8264,17 @@
         <v>26</v>
       </c>
       <c r="N82" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="O82">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="P82">
-        <f t="shared" si="12"/>
-        <v>540</v>
+        <f>ROUND(O82*P$1/5,0)*5</f>
+        <v>650</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R82" t="s">
         <v>2</v>
@@ -7690,13 +8283,13 @@
         <v>3</v>
       </c>
       <c r="T82" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_STADIUM" /&gt;&lt;Set Cost="540"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q82,N82,R82,P82,S82)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_RESEARCH_LAB" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B83">
         <v>330</v>
@@ -7713,7 +8306,7 @@
         <v>285</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G83" t="s">
         <v>2</v>
@@ -7726,17 +8319,17 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_CUIRASSIER" /&gt;&lt;Set Cost="285"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="N83" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="O83">
         <v>540</v>
       </c>
       <c r="P83">
-        <f t="shared" si="12"/>
+        <f>ROUND(O83*P$1/5,0)*5</f>
         <v>650</v>
       </c>
       <c r="Q83" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R83" t="s">
         <v>2</v>
@@ -7745,13 +8338,13 @@
         <v>3</v>
       </c>
       <c r="T83" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_POWER_PLANT" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q83,N83,R83,P83,S83)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AIRPORT" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B84">
         <v>330</v>
@@ -7768,7 +8361,7 @@
         <v>285</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G84" t="s">
         <v>2</v>
@@ -7781,17 +8374,17 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_COLOMBIAN_LLANERO" /&gt;&lt;Set Cost="285"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="N84" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="O84">
         <v>540</v>
       </c>
       <c r="P84">
-        <f t="shared" si="12"/>
+        <f>ROUND(O84*P$1/5,0)*5</f>
         <v>650</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R84" t="s">
         <v>2</v>
@@ -7800,13 +8393,13 @@
         <v>3</v>
       </c>
       <c r="T84" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_RESEARCH_LAB" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q84,N84,R84,P84,S84)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AQUATICS_CENTER" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B85">
         <v>335</v>
@@ -7823,7 +8416,7 @@
         <v>290</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G85" t="s">
         <v>2</v>
@@ -7836,17 +8429,17 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_HUNGARY_HUSZAR" /&gt;&lt;Set Cost="290"/&gt;&lt;/Update&gt;</v>
       </c>
       <c r="N85" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="O85">
-        <v>540</v>
+        <v>650</v>
       </c>
       <c r="P85">
-        <f t="shared" si="12"/>
-        <v>650</v>
+        <f>ROUND(O85*P$1/5,0)*5</f>
+        <v>785</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>293</v>
+        <v>1</v>
       </c>
       <c r="R85" t="s">
         <v>2</v>
@@ -7855,13 +8448,13 @@
         <v>3</v>
       </c>
       <c r="T85" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AIRPORT" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+        <f>_xlfn.CONCAT(Q85,N85,R85,P85,S85)</f>
+        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MANUFACTURING_PLANT" /&gt;&lt;Set Cost="785"/&gt;&lt;/Update&gt;</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B86">
         <v>340</v>
@@ -7878,7 +8471,7 @@
         <v>295</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G86" t="s">
         <v>2</v>
@@ -7890,33 +8483,10 @@
         <f t="shared" si="11"/>
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_RUSSIAN_COSSACK" /&gt;&lt;Set Cost="295"/&gt;&lt;/Update&gt;</v>
       </c>
-      <c r="N86" t="s">
-        <v>232</v>
-      </c>
-      <c r="O86">
-        <v>540</v>
-      </c>
-      <c r="P86">
-        <f t="shared" si="12"/>
-        <v>650</v>
-      </c>
-      <c r="Q86" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="R86" t="s">
-        <v>2</v>
-      </c>
-      <c r="S86" t="s">
-        <v>3</v>
-      </c>
-      <c r="T86" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_AQUATICS_CENTER" /&gt;&lt;Set Cost="650"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B87">
         <v>360</v>
@@ -7933,7 +8503,7 @@
         <v>315</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G87" t="s">
         <v>2</v>
@@ -7945,33 +8515,10 @@
         <f t="shared" si="11"/>
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ENGLISH_REDCOAT" /&gt;&lt;Set Cost="315"/&gt;&lt;/Update&gt;</v>
       </c>
-      <c r="N87" t="s">
-        <v>292</v>
-      </c>
-      <c r="O87">
-        <v>650</v>
-      </c>
-      <c r="P87">
-        <f t="shared" si="12"/>
-        <v>785</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="R87" t="s">
-        <v>2</v>
-      </c>
-      <c r="S87" t="s">
-        <v>3</v>
-      </c>
-      <c r="T87" t="str">
-        <f t="shared" si="13"/>
-        <v>&lt;Update&gt;&lt;Where BuildingType="BUILDING_MANUFACTURING_PLANT" /&gt;&lt;Set Cost="785"/&gt;&lt;/Update&gt;</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B88">
         <v>360</v>
@@ -7988,7 +8535,7 @@
         <v>315</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G88" t="s">
         <v>2</v>
@@ -8001,9 +8548,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_FRENCH_GARDE_IMPERIALE" /&gt;&lt;Set Cost="315"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B89">
         <v>360</v>
@@ -8020,7 +8567,7 @@
         <v>315</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G89" t="s">
         <v>2</v>
@@ -8033,9 +8580,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_LINE_INFANTRY" /&gt;&lt;Set Cost="315"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B90">
         <v>370</v>
@@ -8044,15 +8591,15 @@
         <v>22</v>
       </c>
       <c r="D90">
-        <f t="shared" ref="D90:D120" si="14">ROUND(B90*D$1/5,0)*5</f>
+        <f t="shared" ref="D90:D123" si="14">ROUND(B90*D$1/5,0)*5</f>
         <v>290</v>
       </c>
       <c r="E90">
-        <f t="shared" ref="E90:E120" si="15">ROUND(B90*E$1/5,0)*5</f>
+        <f t="shared" ref="E90:E123" si="15">ROUND(B90*E$1/5,0)*5</f>
         <v>320</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G90" t="s">
         <v>2</v>
@@ -8065,9 +8612,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MEDIC" /&gt;&lt;Set Cost="320"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B91">
         <v>380</v>
@@ -8084,7 +8631,7 @@
         <v>330</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G91" t="s">
         <v>2</v>
@@ -8097,9 +8644,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_IRONCLAD" /&gt;&lt;Set Cost="330"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B92">
         <v>380</v>
@@ -8116,7 +8663,7 @@
         <v>330</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G92" t="s">
         <v>2</v>
@@ -8129,9 +8676,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_RANGER" /&gt;&lt;Set Cost="330"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B93">
         <v>380</v>
@@ -8148,7 +8695,7 @@
         <v>330</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G93" t="s">
         <v>2</v>
@@ -8161,9 +8708,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SCOTTISH_HIGHLANDER" /&gt;&lt;Set Cost="330"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B94">
         <v>385</v>
@@ -8180,7 +8727,7 @@
         <v>335</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G94" t="s">
         <v>2</v>
@@ -8193,9 +8740,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_AMERICAN_ROUGH_RIDER" /&gt;&lt;Set Cost="335"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B95">
         <v>400</v>
@@ -8212,7 +8759,7 @@
         <v>350</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G95" t="s">
         <v>2</v>
@@ -8225,9 +8772,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_AT_CREW" /&gt;&lt;Set Cost="350"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B96">
         <v>420</v>
@@ -8244,7 +8791,7 @@
         <v>365</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G96" t="s">
         <v>2</v>
@@ -8257,9 +8804,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_DRONE" /&gt;&lt;Set Cost="365"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B97">
         <v>430</v>
@@ -8276,7 +8823,7 @@
         <v>375</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G97" t="s">
         <v>2</v>
@@ -8289,9 +8836,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BIPLANE" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B98">
         <v>430</v>
@@ -8308,7 +8855,7 @@
         <v>375</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G98" t="s">
         <v>2</v>
@@ -8321,9 +8868,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_INFANTRY" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B99">
         <v>430</v>
@@ -8340,7 +8887,7 @@
         <v>375</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G99" t="s">
         <v>2</v>
@@ -8353,9 +8900,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ARTILLERY" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B100">
         <v>430</v>
@@ -8372,7 +8919,7 @@
         <v>375</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G100" t="s">
         <v>2</v>
@@ -8385,9 +8932,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BATTLESHIP" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B101">
         <v>430</v>
@@ -8404,7 +8951,7 @@
         <v>375</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G101" t="s">
         <v>2</v>
@@ -8417,9 +8964,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BRAZILIAN_MINAS_GERAES" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B102">
         <v>430</v>
@@ -8436,7 +8983,7 @@
         <v>375</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G102" t="s">
         <v>2</v>
@@ -8449,9 +8996,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_GERMAN_UBOAT" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B103">
         <v>430</v>
@@ -8468,7 +9015,7 @@
         <v>375</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G103" t="s">
         <v>2</v>
@@ -8481,9 +9028,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_DIGGER" /&gt;&lt;Set Cost="375"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B104">
         <v>450</v>
@@ -8500,7 +9047,7 @@
         <v>390</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G104" t="s">
         <v>2</v>
@@ -8513,9 +9060,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SUPPLY_CONVOY" /&gt;&lt;Set Cost="390"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B105">
         <v>455</v>
@@ -8532,7 +9079,7 @@
         <v>395</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G105" t="s">
         <v>2</v>
@@ -8545,9 +9092,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ANTIAIR_GUN" /&gt;&lt;Set Cost="395"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B106">
         <v>480</v>
@@ -8564,7 +9111,7 @@
         <v>420</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G106" t="s">
         <v>2</v>
@@ -8577,9 +9124,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SUBMARINE" /&gt;&lt;Set Cost="420"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B107">
         <v>480</v>
@@ -8596,7 +9143,7 @@
         <v>420</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G107" t="s">
         <v>2</v>
@@ -8609,9 +9156,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_TANK" /&gt;&lt;Set Cost="420"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B108">
         <v>520</v>
@@ -8628,7 +9175,7 @@
         <v>450</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G108" t="s">
         <v>2</v>
@@ -8641,9 +9188,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_FIGHTER" /&gt;&lt;Set Cost="450"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B109">
         <v>520</v>
@@ -8660,7 +9207,7 @@
         <v>450</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G109" t="s">
         <v>2</v>
@@ -8673,9 +9220,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_AMERICAN_P51" /&gt;&lt;Set Cost="450"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B110">
         <v>520</v>
@@ -8692,7 +9239,7 @@
         <v>450</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G110" t="s">
         <v>2</v>
@@ -8705,9 +9252,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_SPEC_OPS" /&gt;&lt;Set Cost="450"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B111">
         <v>540</v>
@@ -8724,7 +9271,7 @@
         <v>470</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G111" t="s">
         <v>2</v>
@@ -8737,9 +9284,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MACHINE_GUN" /&gt;&lt;Set Cost="470"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B112">
         <v>540</v>
@@ -8756,7 +9303,7 @@
         <v>470</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G112" t="s">
         <v>2</v>
@@ -8769,9 +9316,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_AIRCRAFT_CARRIER" /&gt;&lt;Set Cost="470"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B113">
         <v>540</v>
@@ -8788,7 +9335,7 @@
         <v>470</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G113" t="s">
         <v>2</v>
@@ -8801,9 +9348,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_DESTROYER" /&gt;&lt;Set Cost="470"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B114">
         <v>560</v>
@@ -8820,7 +9367,7 @@
         <v>485</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G114" t="s">
         <v>2</v>
@@ -8833,9 +9380,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_BOMBER" /&gt;&lt;Set Cost="485"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B115">
         <v>580</v>
@@ -8852,7 +9399,7 @@
         <v>505</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G115" t="s">
         <v>2</v>
@@ -8865,9 +9412,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MODERN_AT" /&gt;&lt;Set Cost="505"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B116">
         <v>590</v>
@@ -8884,7 +9431,7 @@
         <v>515</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G116" t="s">
         <v>2</v>
@@ -8897,9 +9444,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MOBILE_SAM" /&gt;&lt;Set Cost="515"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B117">
         <v>600</v>
@@ -8916,7 +9463,7 @@
         <v>520</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G117" t="s">
         <v>2</v>
@@ -8929,9 +9476,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_HELICOPTER" /&gt;&lt;Set Cost="520"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B118">
         <v>650</v>
@@ -8948,7 +9495,7 @@
         <v>565</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G118" t="s">
         <v>2</v>
@@ -8961,9 +9508,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MECHANIZED_INFANTRY" /&gt;&lt;Set Cost="565"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B119">
         <v>650</v>
@@ -8980,7 +9527,7 @@
         <v>565</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G119" t="s">
         <v>2</v>
@@ -8993,9 +9540,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_JET_FIGHTER" /&gt;&lt;Set Cost="565"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B120">
         <v>680</v>
@@ -9012,7 +9559,7 @@
         <v>590</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G120" t="s">
         <v>2</v>
@@ -9025,9 +9572,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_NUCLEAR_SUBMARINE" /&gt;&lt;Set Cost="590"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B121">
         <v>680</v>
@@ -9036,15 +9583,15 @@
         <v>28</v>
       </c>
       <c r="D121">
-        <f>ROUND(B121*D$1/5,0)*5</f>
+        <f t="shared" si="14"/>
         <v>530</v>
       </c>
       <c r="E121">
-        <f>ROUND(B121*E$1/5,0)*5</f>
+        <f t="shared" si="15"/>
         <v>590</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G121" t="s">
         <v>2</v>
@@ -9057,9 +9604,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_ROCKET_ARTILLERY" /&gt;&lt;Set Cost="590"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B122">
         <v>680</v>
@@ -9068,15 +9615,15 @@
         <v>28</v>
       </c>
       <c r="D122">
-        <f>ROUND(B122*D$1/5,0)*5</f>
+        <f t="shared" si="14"/>
         <v>530</v>
       </c>
       <c r="E122">
-        <f>ROUND(B122*E$1/5,0)*5</f>
+        <f t="shared" si="15"/>
         <v>590</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G122" t="s">
         <v>2</v>
@@ -9089,9 +9636,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MISSILE_CRUISER" /&gt;&lt;Set Cost="590"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B123">
         <v>680</v>
@@ -9100,15 +9647,15 @@
         <v>28</v>
       </c>
       <c r="D123">
-        <f>ROUND(B123*D$1/5,0)*5</f>
+        <f t="shared" si="14"/>
         <v>530</v>
       </c>
       <c r="E123">
-        <f>ROUND(B123*E$1/5,0)*5</f>
+        <f t="shared" si="15"/>
         <v>590</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>284</v>
+        <v>71</v>
       </c>
       <c r="G123" t="s">
         <v>2</v>
@@ -9121,9 +9668,9 @@
         <v>&lt;Update&gt;&lt;Where UnitType="UNIT_MODERN_ARMOR" /&gt;&lt;Set Cost="590"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" t="s">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="B125">
         <v>40</v>
@@ -9153,9 +9700,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_TRADER" /&gt;&lt;Set Cost="35"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9">
       <c r="A126" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="B126">
         <v>50</v>
@@ -9185,9 +9732,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_BUILDER" /&gt;&lt;Set Cost="45"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>282</v>
       </c>
       <c r="B127">
         <v>120</v>
@@ -9217,9 +9764,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_GURU" /&gt;&lt;Set Cost="105"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" t="s">
-        <v>115</v>
+        <v>283</v>
       </c>
       <c r="B128">
         <v>75</v>
@@ -9249,9 +9796,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_MISSIONARY" /&gt;&lt;Set Cost="65"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="B129">
         <v>75</v>
@@ -9281,9 +9828,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_INQUISITOR" /&gt;&lt;Set Cost="65"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" t="s">
-        <v>119</v>
+        <v>285</v>
       </c>
       <c r="B130">
         <v>80</v>
@@ -9313,9 +9860,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_SETTLER" /&gt;&lt;Set Cost="70"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9">
       <c r="A131" t="s">
-        <v>183</v>
+        <v>286</v>
       </c>
       <c r="B131">
         <v>200</v>
@@ -9345,9 +9892,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_APOSTLE" /&gt;&lt;Set Cost="175"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9">
       <c r="A132" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="B132">
         <v>300</v>
@@ -9377,9 +9924,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_ROCK_BAND" /&gt;&lt;Set Cost="260"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9">
       <c r="A133" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="B133">
         <v>300</v>
@@ -9409,9 +9956,9 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_NATURALIST" /&gt;&lt;Set Cost="260"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9">
       <c r="A134" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="B134">
         <v>400</v>
@@ -9441,152 +9988,152 @@
         <v>&lt;Update&gt;&lt;Where BuildingType="UNIT_ARCHAEOLOGIST" /&gt;&lt;Set Cost="350"/&gt;&lt;/Update&gt;</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>280</v>
       </c>
       <c r="B136">
         <v>40</v>
       </c>
       <c r="C136" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E136">
         <v>400</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" t="s">
-        <v>119</v>
+        <v>285</v>
       </c>
       <c r="B137">
         <v>80</v>
       </c>
       <c r="C137" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E137">
         <v>40</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" t="s">
-        <v>87</v>
+        <v>281</v>
       </c>
       <c r="B138">
         <v>50</v>
       </c>
       <c r="C138" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E138">
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9">
       <c r="A139" s="1" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B139">
         <v>75</v>
       </c>
       <c r="C139" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E139">
         <v>10</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9">
       <c r="A140" t="s">
-        <v>183</v>
+        <v>286</v>
       </c>
       <c r="B140">
         <v>200</v>
       </c>
       <c r="C140" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E140">
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" t="s">
-        <v>117</v>
+        <v>284</v>
       </c>
       <c r="B141">
         <v>75</v>
       </c>
       <c r="C141" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E141">
         <v>10</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>282</v>
       </c>
       <c r="B142">
         <v>120</v>
       </c>
       <c r="C142" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E142">
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B143">
         <v>225</v>
       </c>
       <c r="C143" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E143">
         <v>75</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="B144">
         <v>300</v>
       </c>
       <c r="C144" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E144">
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>238</v>
+        <v>287</v>
       </c>
       <c r="B145">
         <v>300</v>
       </c>
       <c r="C145" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="E145">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:P87">
+  <sortState ref="N2:P87">
     <sortCondition ref="O2:O87"/>
   </sortState>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>